--- a/df_pivot.xlsx
+++ b/df_pivot.xlsx
@@ -541,34 +541,34 @@
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
+          <t>ePset_abstractBIM.PredefinedType</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>ePset_abstractBIM.IsExternal</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>ePset_abstractBIM.Spaces</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>ePset_abstractBIM.SpacesLongName</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>ePset_abstractBIM.SpacesName</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
           <t>Pset_CoveringCommon.IsExternal</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>ePset_abstractBIM.PredefinedType</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>ePset_abstractBIM.IsExternal</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>ePset_abstractBIM.Spaces</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>ePset_abstractBIM.SpacesLongName</t>
-        </is>
-      </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>ePset_abstractBIM.SpacesName</t>
-        </is>
-      </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>Pset_SpatialData.BuildingStory</t>
@@ -926,25 +926,25 @@
       </c>
       <c r="CV1" s="1" t="inlineStr">
         <is>
-          <t>__pivot_7.939</t>
+          <t>__pivot_7.94</t>
         </is>
       </c>
       <c r="CW1" s="1" t="inlineStr">
         <is>
-          <t>__pivot_11.947</t>
+          <t>__pivot_11.948</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1215</v>
+        <v>1191</v>
       </c>
       <c r="B2" t="n">
-        <v>1209</v>
+        <v>1186</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>1R$FLavrj8G9Rxnz3lVckG</t>
+          <t>3Hh_lnoOjFseiPP$fBJdTk</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -964,11 +964,11 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>LUF:342799</t>
+          <t>LUF:342961</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>1215</v>
+        <v>1191</v>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
@@ -996,11 +996,11 @@
       <c r="AB2" t="inlineStr"/>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>EG</t>
+          <t>OG1</t>
         </is>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>2.998</v>
       </c>
       <c r="AE2" t="inlineStr"/>
       <c r="AF2" t="inlineStr"/>
@@ -1107,20 +1107,20 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>3$FY_ljDfBsweJfZwnfjOk</t>
+          <t>0b93QOWH141xpbKCpGErNs</t>
         </is>
       </c>
       <c r="CE2" t="n">
-        <v>3</v>
+        <v>4.942</v>
       </c>
       <c r="CF2" t="n">
-        <v>58.6046173021893</v>
+        <v>7.38232192035912</v>
       </c>
       <c r="CG2" t="n">
-        <v>29.7644175</v>
+        <v>2.3140405</v>
       </c>
       <c r="CH2" t="n">
-        <v>89.29325249999999</v>
+        <v>11.435988151</v>
       </c>
       <c r="CI2" t="inlineStr"/>
       <c r="CJ2" t="inlineStr"/>
@@ -1142,10 +1142,10 @@
         <v>0</v>
       </c>
       <c r="CT2" t="n">
-        <v>29.7644175</v>
+        <v>0</v>
       </c>
       <c r="CU2" t="n">
-        <v>0</v>
+        <v>2.3140405</v>
       </c>
       <c r="CV2" t="n">
         <v>0</v>
@@ -1156,14 +1156,14 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>1216</v>
+        <v>1192</v>
       </c>
       <c r="B3" t="n">
-        <v>1210</v>
+        <v>1187</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0CIMZOOqj8GukY8gSKgU97</t>
+          <t>2P3Mbts9P06BZqiOxGDRsK</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -1183,11 +1183,11 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>LUF:342961</t>
+          <t>LUF:343164</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>1216</v>
+        <v>1192</v>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
@@ -1215,11 +1215,11 @@
       <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>OG1</t>
+          <t>OG2</t>
         </is>
       </c>
       <c r="AD3" t="n">
-        <v>2.998</v>
+        <v>7.94</v>
       </c>
       <c r="AE3" t="inlineStr"/>
       <c r="AF3" t="inlineStr"/>
@@ -1326,11 +1326,11 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>0b93QOWH141xpbKCpGErNs</t>
+          <t>0b93QOWH141xpbKCpGEr8x</t>
         </is>
       </c>
       <c r="CE3" t="n">
-        <v>4.941</v>
+        <v>4.008</v>
       </c>
       <c r="CF3" t="n">
         <v>7.38232192035912</v>
@@ -1339,7 +1339,7 @@
         <v>2.3140405</v>
       </c>
       <c r="CH3" t="n">
-        <v>11.4336741105</v>
+        <v>9.274674323999999</v>
       </c>
       <c r="CI3" t="inlineStr"/>
       <c r="CJ3" t="inlineStr"/>
@@ -1364,10 +1364,10 @@
         <v>0</v>
       </c>
       <c r="CU3" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV3" t="n">
         <v>2.3140405</v>
-      </c>
-      <c r="CV3" t="n">
-        <v>0</v>
       </c>
       <c r="CW3" t="n">
         <v>0</v>
@@ -1375,14 +1375,14 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>1217</v>
+        <v>1193</v>
       </c>
       <c r="B4" t="n">
-        <v>1211</v>
+        <v>1188</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>18j2PWjBz3nhKzSkJrvM7d</t>
+          <t>39ETwZKMDAou$vKVot7pYG</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1402,11 +1402,11 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>LUF:343164</t>
+          <t>LUF:343294</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>1217</v>
+        <v>1193</v>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
@@ -1434,11 +1434,11 @@
       <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>OG2</t>
+          <t>OG3</t>
         </is>
       </c>
       <c r="AD4" t="n">
-        <v>7.939</v>
+        <v>11.948</v>
       </c>
       <c r="AE4" t="inlineStr"/>
       <c r="AF4" t="inlineStr"/>
@@ -1545,20 +1545,20 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>0b93QOWH141xpbKCpGEr8x</t>
+          <t>3ol_0stLL7q8pSNseENpkb</t>
         </is>
       </c>
       <c r="CE4" t="n">
-        <v>4.008</v>
+        <v>2.522</v>
       </c>
       <c r="CF4" t="n">
-        <v>7.38232192035912</v>
+        <v>7.49144557435166</v>
       </c>
       <c r="CG4" t="n">
-        <v>2.3140405</v>
+        <v>2.357719</v>
       </c>
       <c r="CH4" t="n">
-        <v>9.274674323999999</v>
+        <v>5.946167318</v>
       </c>
       <c r="CI4" t="inlineStr"/>
       <c r="CJ4" t="inlineStr"/>
@@ -1586,22 +1586,22 @@
         <v>0</v>
       </c>
       <c r="CV4" t="n">
-        <v>2.3140405</v>
+        <v>0</v>
       </c>
       <c r="CW4" t="n">
-        <v>0</v>
+        <v>2.357719</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>1218</v>
+        <v>1194</v>
       </c>
       <c r="B5" t="n">
-        <v>1212</v>
+        <v>1183</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0wtQ7wfjD5FPd24jrI75yq</t>
+          <t>0flQ6A_KT1au1P6tc3jqMc</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1621,11 +1621,11 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>LUF:343294</t>
+          <t>TRH:341682</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>1218</v>
+        <v>1194</v>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
@@ -1653,11 +1653,11 @@
       <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>OG3</t>
+          <t>UG2</t>
         </is>
       </c>
       <c r="AD5" t="n">
-        <v>11.947</v>
+        <v>-8.199999999999999</v>
       </c>
       <c r="AE5" t="inlineStr"/>
       <c r="AF5" t="inlineStr"/>
@@ -1713,7 +1713,7 @@
       <c r="BR5" t="inlineStr"/>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>LUF</t>
+          <t>TRH</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
@@ -1728,7 +1728,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>Luftraum</t>
+          <t>Treppenhaus</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -1738,7 +1738,7 @@
       </c>
       <c r="BX5" t="inlineStr">
         <is>
-          <t>LUF  -  Luftraum</t>
+          <t>TRH  -  Treppenhaus</t>
         </is>
       </c>
       <c r="BY5" t="inlineStr">
@@ -1747,7 +1747,7 @@
         </is>
       </c>
       <c r="BZ5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CA5" t="n">
         <v>1</v>
@@ -1764,22 +1764,26 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>3ol_0stLL7q8pSNseENpkb</t>
+          <t>3VbCMl1_928hbAKPG5Knl1</t>
         </is>
       </c>
       <c r="CE5" t="n">
-        <v>2.523</v>
+        <v>4.12</v>
       </c>
       <c r="CF5" t="n">
-        <v>7.49144557435166</v>
+        <v>11.5222748736684</v>
       </c>
       <c r="CG5" t="n">
-        <v>2.357719</v>
+        <v>10.428806</v>
       </c>
       <c r="CH5" t="n">
-        <v>5.948525037</v>
-      </c>
-      <c r="CI5" t="inlineStr"/>
+        <v>42.96668072</v>
+      </c>
+      <c r="CI5" t="inlineStr">
+        <is>
+          <t>VF</t>
+        </is>
+      </c>
       <c r="CJ5" t="inlineStr"/>
       <c r="CK5" t="inlineStr"/>
       <c r="CL5" t="inlineStr"/>
@@ -1789,11 +1793,11 @@
       <c r="CP5" t="inlineStr"/>
       <c r="CQ5" t="inlineStr">
         <is>
-          <t>Allgemein_LUF</t>
+          <t>Allgemein_TRH</t>
         </is>
       </c>
       <c r="CR5" t="n">
-        <v>0</v>
+        <v>10.428806</v>
       </c>
       <c r="CS5" t="n">
         <v>0</v>
@@ -1808,19 +1812,19 @@
         <v>0</v>
       </c>
       <c r="CW5" t="n">
-        <v>2.357719</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>1219</v>
+        <v>1195</v>
       </c>
       <c r="B6" t="n">
-        <v>1212</v>
+        <v>1183</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2Ru4iRmYDDDfo5eLHGZ8RE</t>
+          <t>2F6s1tVBjDqQjhbB3E6WYb</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1840,11 +1844,11 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>KOR:343282</t>
+          <t>TRH:341685</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>1219</v>
+        <v>1195</v>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
@@ -1872,11 +1876,11 @@
       <c r="AB6" t="inlineStr"/>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>OG3</t>
+          <t>UG2</t>
         </is>
       </c>
       <c r="AD6" t="n">
-        <v>11.947</v>
+        <v>-8.199999999999999</v>
       </c>
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr"/>
@@ -1932,7 +1936,7 @@
       <c r="BR6" t="inlineStr"/>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>KOR</t>
+          <t>TRH</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
@@ -1947,7 +1951,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>Korridor</t>
+          <t>Treppenhaus</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -1957,7 +1961,7 @@
       </c>
       <c r="BX6" t="inlineStr">
         <is>
-          <t>KOR  -  Korridor</t>
+          <t>TRH  -  Treppenhaus</t>
         </is>
       </c>
       <c r="BY6" t="inlineStr">
@@ -1983,20 +1987,20 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>3ol_0stLL7q8pSNseENpkf</t>
+          <t>3VbCMl1_928hbAKPG5Knl6</t>
         </is>
       </c>
       <c r="CE6" t="n">
-        <v>2.522</v>
+        <v>4.12</v>
       </c>
       <c r="CF6" t="n">
-        <v>24.6411125862649</v>
+        <v>30.3639272858965</v>
       </c>
       <c r="CG6" t="n">
-        <v>13.547317</v>
+        <v>32.464858</v>
       </c>
       <c r="CH6" t="n">
-        <v>34.166333474</v>
+        <v>133.75521496</v>
       </c>
       <c r="CI6" t="inlineStr">
         <is>
@@ -2012,11 +2016,11 @@
       <c r="CP6" t="inlineStr"/>
       <c r="CQ6" t="inlineStr">
         <is>
-          <t>Allgemein_KOR</t>
+          <t>Allgemein_TRH</t>
         </is>
       </c>
       <c r="CR6" t="n">
-        <v>0</v>
+        <v>32.464858</v>
       </c>
       <c r="CS6" t="n">
         <v>0</v>
@@ -2031,19 +2035,19 @@
         <v>0</v>
       </c>
       <c r="CW6" t="n">
-        <v>13.547317</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>1220</v>
+        <v>1196</v>
       </c>
       <c r="B7" t="n">
-        <v>1207</v>
+        <v>1184</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>3Q30KcAwrFjgFId43DWY8P</t>
+          <t>1ob0Dr3Tb3me5ixnzVhldr</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -2063,11 +2067,11 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>TRH:341682</t>
+          <t>TRH:342381</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>1220</v>
+        <v>1196</v>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
@@ -2095,11 +2099,11 @@
       <c r="AB7" t="inlineStr"/>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>UG2</t>
+          <t>UG1</t>
         </is>
       </c>
       <c r="AD7" t="n">
-        <v>-8.199999999999999</v>
+        <v>-3.78</v>
       </c>
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr"/>
@@ -2206,20 +2210,20 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>3VbCMl1_928hbAKPG5Knl1</t>
+          <t>1QH5Axl111J9SJj2E3W4w1</t>
         </is>
       </c>
       <c r="CE7" t="n">
-        <v>4.121</v>
+        <v>3.42</v>
       </c>
       <c r="CF7" t="n">
-        <v>10.4407453756904</v>
+        <v>30.8626322671356</v>
       </c>
       <c r="CG7" t="n">
-        <v>6.8130725</v>
+        <v>58.794787</v>
       </c>
       <c r="CH7" t="n">
-        <v>28.0766717725</v>
+        <v>201.07817154</v>
       </c>
       <c r="CI7" t="inlineStr">
         <is>
@@ -2239,10 +2243,10 @@
         </is>
       </c>
       <c r="CR7" t="n">
-        <v>6.8130725</v>
+        <v>0</v>
       </c>
       <c r="CS7" t="n">
-        <v>0</v>
+        <v>58.794787</v>
       </c>
       <c r="CT7" t="n">
         <v>0</v>
@@ -2259,14 +2263,14 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>1221</v>
+        <v>1197</v>
       </c>
       <c r="B8" t="n">
-        <v>1207</v>
+        <v>1183</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>34G_SBUtD7Bx_aSDXbyBOH</t>
+          <t>0WugxlnUz8xx2oGJ_ePbye</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -2286,11 +2290,11 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>TRH:341685</t>
+          <t>LUF:340252</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>1221</v>
+        <v>1197</v>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
@@ -2378,7 +2382,7 @@
       <c r="BR8" t="inlineStr"/>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>TRH</t>
+          <t>LUF</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
@@ -2393,7 +2397,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>Treppenhaus</t>
+          <t>Luftraum</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -2403,7 +2407,7 @@
       </c>
       <c r="BX8" t="inlineStr">
         <is>
-          <t>TRH  -  Treppenhaus</t>
+          <t>LUF  -  Luftraum</t>
         </is>
       </c>
       <c r="BY8" t="inlineStr">
@@ -2412,7 +2416,7 @@
         </is>
       </c>
       <c r="BZ8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CA8" t="n">
         <v>1</v>
@@ -2429,26 +2433,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>3VbCMl1_928hbAKPG5Knl6</t>
+          <t>3VbCMl1_928hbAKPG5Knnl</t>
         </is>
       </c>
       <c r="CE8" t="n">
-        <v>4.121</v>
+        <v>4.42</v>
       </c>
       <c r="CF8" t="n">
-        <v>30.404276140697</v>
+        <v>7.38232192035912</v>
       </c>
       <c r="CG8" t="n">
-        <v>32.270022</v>
+        <v>2.3140405</v>
       </c>
       <c r="CH8" t="n">
-        <v>132.984760662</v>
-      </c>
-      <c r="CI8" t="inlineStr">
-        <is>
-          <t>VF</t>
-        </is>
-      </c>
+        <v>10.22805901</v>
+      </c>
+      <c r="CI8" t="inlineStr"/>
       <c r="CJ8" t="inlineStr"/>
       <c r="CK8" t="inlineStr"/>
       <c r="CL8" t="inlineStr"/>
@@ -2458,11 +2458,11 @@
       <c r="CP8" t="inlineStr"/>
       <c r="CQ8" t="inlineStr">
         <is>
-          <t>Allgemein_TRH</t>
+          <t>Allgemein_LUF</t>
         </is>
       </c>
       <c r="CR8" t="n">
-        <v>32.270022</v>
+        <v>2.3140405</v>
       </c>
       <c r="CS8" t="n">
         <v>0</v>
@@ -2482,14 +2482,14 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>1222</v>
+        <v>1198</v>
       </c>
       <c r="B9" t="n">
-        <v>1208</v>
+        <v>1184</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>11GLlly7bCgPkVa3553rnS</t>
+          <t>1TuiyJHazFPP354k0XGOop</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2509,11 +2509,11 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>TRH:342381</t>
+          <t>LUF:342420</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>1222</v>
+        <v>1198</v>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
@@ -2601,7 +2601,7 @@
       <c r="BR9" t="inlineStr"/>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>TRH</t>
+          <t>LUF</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
@@ -2616,7 +2616,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>Treppenhaus</t>
+          <t>Luftraum</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="BX9" t="inlineStr">
         <is>
-          <t>TRH  -  Treppenhaus</t>
+          <t>LUF  -  Luftraum</t>
         </is>
       </c>
       <c r="BY9" t="inlineStr">
@@ -2635,7 +2635,7 @@
         </is>
       </c>
       <c r="BZ9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CA9" t="n">
         <v>1</v>
@@ -2652,26 +2652,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>1QH5Axl111J9SJj2E3W4w1</t>
+          <t>1QH5Axl111J9SJj2E3W4vu</t>
         </is>
       </c>
       <c r="CE9" t="n">
-        <v>3.421</v>
+        <v>3.42</v>
       </c>
       <c r="CF9" t="n">
-        <v>30.8427134126076</v>
+        <v>7.38098313865425</v>
       </c>
       <c r="CG9" t="n">
-        <v>58.7912815</v>
+        <v>2.312567</v>
       </c>
       <c r="CH9" t="n">
-        <v>201.1249740115</v>
-      </c>
-      <c r="CI9" t="inlineStr">
-        <is>
-          <t>VF</t>
-        </is>
-      </c>
+        <v>7.90897914</v>
+      </c>
+      <c r="CI9" t="inlineStr"/>
       <c r="CJ9" t="inlineStr"/>
       <c r="CK9" t="inlineStr"/>
       <c r="CL9" t="inlineStr"/>
@@ -2681,14 +2677,14 @@
       <c r="CP9" t="inlineStr"/>
       <c r="CQ9" t="inlineStr">
         <is>
-          <t>Allgemein_TRH</t>
+          <t>Allgemein_LUF</t>
         </is>
       </c>
       <c r="CR9" t="n">
         <v>0</v>
       </c>
       <c r="CS9" t="n">
-        <v>58.7912815</v>
+        <v>2.312567</v>
       </c>
       <c r="CT9" t="n">
         <v>0</v>
@@ -2705,14 +2701,14 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>1223</v>
+        <v>1199</v>
       </c>
       <c r="B10" t="n">
-        <v>1207</v>
+        <v>1185</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>13LOp07jD0lfjp1Ds2xiaX</t>
+          <t>049y1zqcb029syIWXEZkws</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2732,11 +2728,11 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>LUF:340252</t>
+          <t>LUF:342799</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>1223</v>
+        <v>1199</v>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
@@ -2764,11 +2760,11 @@
       <c r="AB10" t="inlineStr"/>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>UG2</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="AD10" t="n">
-        <v>-8.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="inlineStr"/>
       <c r="AF10" t="inlineStr"/>
@@ -2875,20 +2871,20 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>3VbCMl1_928hbAKPG5Knnl</t>
+          <t>3$FY_ljDfBsweJfZwnfjOk</t>
         </is>
       </c>
       <c r="CE10" t="n">
-        <v>4.42</v>
+        <v>3</v>
       </c>
       <c r="CF10" t="n">
-        <v>7.38232192035912</v>
+        <v>58.6046173021893</v>
       </c>
       <c r="CG10" t="n">
-        <v>2.3140405</v>
+        <v>29.7644175</v>
       </c>
       <c r="CH10" t="n">
-        <v>10.22805901</v>
+        <v>89.29325249999999</v>
       </c>
       <c r="CI10" t="inlineStr"/>
       <c r="CJ10" t="inlineStr"/>
@@ -2904,13 +2900,13 @@
         </is>
       </c>
       <c r="CR10" t="n">
-        <v>2.3140405</v>
+        <v>0</v>
       </c>
       <c r="CS10" t="n">
         <v>0</v>
       </c>
       <c r="CT10" t="n">
-        <v>0</v>
+        <v>29.7644175</v>
       </c>
       <c r="CU10" t="n">
         <v>0</v>
@@ -2924,14 +2920,14 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>1224</v>
+        <v>1200</v>
       </c>
       <c r="B11" t="n">
-        <v>1208</v>
+        <v>1185</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>3BN76u7jD8SONfck_e054E</t>
+          <t>3lSeJHANz4JwuuWWVWxbUH</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2951,11 +2947,11 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>LUF:342420</t>
+          <t>VRF:342787</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>1224</v>
+        <v>1200</v>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
@@ -2983,11 +2979,11 @@
       <c r="AB11" t="inlineStr"/>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>UG1</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="AD11" t="n">
-        <v>-3.78</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="inlineStr"/>
       <c r="AF11" t="inlineStr"/>
@@ -3043,7 +3039,7 @@
       <c r="BR11" t="inlineStr"/>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>LUF</t>
+          <t>VRF</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
@@ -3058,7 +3054,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>Luftraum</t>
+          <t>Verkehrsfläche</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -3068,7 +3064,7 @@
       </c>
       <c r="BX11" t="inlineStr">
         <is>
-          <t>LUF  -  Luftraum</t>
+          <t>VRF  -  Verkehrsfläche</t>
         </is>
       </c>
       <c r="BY11" t="inlineStr">
@@ -3077,7 +3073,7 @@
         </is>
       </c>
       <c r="BZ11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CA11" t="n">
         <v>1</v>
@@ -3094,22 +3090,26 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>1QH5Axl111J9SJj2E3W4vu</t>
+          <t>3$FY_ljDfBsweJfZwnfjOY</t>
         </is>
       </c>
       <c r="CE11" t="n">
-        <v>3.421</v>
+        <v>3</v>
       </c>
       <c r="CF11" t="n">
-        <v>7.38098313865425</v>
+        <v>7.99949280466301</v>
       </c>
       <c r="CG11" t="n">
-        <v>2.312567</v>
+        <v>3.4365005</v>
       </c>
       <c r="CH11" t="n">
-        <v>7.911291707</v>
-      </c>
-      <c r="CI11" t="inlineStr"/>
+        <v>10.3095015</v>
+      </c>
+      <c r="CI11" t="inlineStr">
+        <is>
+          <t>VF</t>
+        </is>
+      </c>
       <c r="CJ11" t="inlineStr"/>
       <c r="CK11" t="inlineStr"/>
       <c r="CL11" t="inlineStr"/>
@@ -3119,17 +3119,17 @@
       <c r="CP11" t="inlineStr"/>
       <c r="CQ11" t="inlineStr">
         <is>
-          <t>Allgemein_LUF</t>
+          <t>Allgemein_VRF</t>
         </is>
       </c>
       <c r="CR11" t="n">
         <v>0</v>
       </c>
       <c r="CS11" t="n">
-        <v>2.312567</v>
+        <v>0</v>
       </c>
       <c r="CT11" t="n">
-        <v>0</v>
+        <v>3.4365005</v>
       </c>
       <c r="CU11" t="n">
         <v>0</v>
@@ -3143,14 +3143,14 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>1225</v>
+        <v>1201</v>
       </c>
       <c r="B12" t="n">
-        <v>1209</v>
+        <v>1185</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0jRMZ$SnH9ouX0ZQEwstxo</t>
+          <t>1s_RuZ0k90YAlXWhJ4lnX8</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -3170,11 +3170,11 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>VRF:342787</t>
+          <t>VRF:342790</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>1225</v>
+        <v>1201</v>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
@@ -3313,20 +3313,20 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>3$FY_ljDfBsweJfZwnfjOY</t>
+          <t>3$FY_ljDfBsweJfZwnfjOd</t>
         </is>
       </c>
       <c r="CE12" t="n">
         <v>3</v>
       </c>
       <c r="CF12" t="n">
-        <v>7.99949280466301</v>
+        <v>8.511555999555499</v>
       </c>
       <c r="CG12" t="n">
-        <v>3.4365005</v>
+        <v>4.141197</v>
       </c>
       <c r="CH12" t="n">
-        <v>10.3095015</v>
+        <v>12.423591</v>
       </c>
       <c r="CI12" t="inlineStr">
         <is>
@@ -3352,7 +3352,7 @@
         <v>0</v>
       </c>
       <c r="CT12" t="n">
-        <v>3.4365005</v>
+        <v>4.141197</v>
       </c>
       <c r="CU12" t="n">
         <v>0</v>
@@ -3366,14 +3366,14 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>1226</v>
+        <v>1202</v>
       </c>
       <c r="B13" t="n">
-        <v>1209</v>
+        <v>1183</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>1830E3dHD5f9qhMIKx9HB6</t>
+          <t>24xm6C08LB6PmPlweCGB8I</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -3393,11 +3393,11 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>VRF:342790</t>
+          <t>KOR:340508</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>1226</v>
+        <v>1202</v>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
@@ -3425,11 +3425,11 @@
       <c r="AB13" t="inlineStr"/>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>EG</t>
+          <t>UG2</t>
         </is>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>-8.199999999999999</v>
       </c>
       <c r="AE13" t="inlineStr"/>
       <c r="AF13" t="inlineStr"/>
@@ -3485,7 +3485,7 @@
       <c r="BR13" t="inlineStr"/>
       <c r="BS13" t="inlineStr">
         <is>
-          <t>VRF</t>
+          <t>KOR</t>
         </is>
       </c>
       <c r="BT13" t="inlineStr">
@@ -3500,7 +3500,7 @@
       </c>
       <c r="BV13" t="inlineStr">
         <is>
-          <t>Verkehrsfläche</t>
+          <t>Korridor</t>
         </is>
       </c>
       <c r="BW13" t="inlineStr">
@@ -3510,7 +3510,7 @@
       </c>
       <c r="BX13" t="inlineStr">
         <is>
-          <t>VRF  -  Verkehrsfläche</t>
+          <t>KOR  -  Korridor</t>
         </is>
       </c>
       <c r="BY13" t="inlineStr">
@@ -3536,20 +3536,20 @@
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>3$FY_ljDfBsweJfZwnfjOd</t>
+          <t>3VbCMl1_928hbAKPG5Knzl</t>
         </is>
       </c>
       <c r="CE13" t="n">
-        <v>3</v>
+        <v>4.12</v>
       </c>
       <c r="CF13" t="n">
-        <v>8.511555999555499</v>
+        <v>20.2968268134622</v>
       </c>
       <c r="CG13" t="n">
-        <v>4.141197</v>
+        <v>10.7493655</v>
       </c>
       <c r="CH13" t="n">
-        <v>12.423591</v>
+        <v>44.28738586</v>
       </c>
       <c r="CI13" t="inlineStr">
         <is>
@@ -3565,17 +3565,17 @@
       <c r="CP13" t="inlineStr"/>
       <c r="CQ13" t="inlineStr">
         <is>
-          <t>Allgemein_VRF</t>
+          <t>Allgemein_KOR</t>
         </is>
       </c>
       <c r="CR13" t="n">
-        <v>0</v>
+        <v>10.7493655</v>
       </c>
       <c r="CS13" t="n">
         <v>0</v>
       </c>
       <c r="CT13" t="n">
-        <v>4.141197</v>
+        <v>0</v>
       </c>
       <c r="CU13" t="n">
         <v>0</v>
@@ -3589,14 +3589,14 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>1227</v>
+        <v>1203</v>
       </c>
       <c r="B14" t="n">
-        <v>1207</v>
+        <v>1184</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>0emPRSOwnDOOTgYleM3B_A</t>
+          <t>0zR70dM_L5hgHRsQfW3Yo7</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3616,11 +3616,11 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>KOR:340508</t>
+          <t>KOR:342423</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>1227</v>
+        <v>1203</v>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
@@ -3648,11 +3648,11 @@
       <c r="AB14" t="inlineStr"/>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>UG2</t>
+          <t>UG1</t>
         </is>
       </c>
       <c r="AD14" t="n">
-        <v>-8.199999999999999</v>
+        <v>-3.78</v>
       </c>
       <c r="AE14" t="inlineStr"/>
       <c r="AF14" t="inlineStr"/>
@@ -3759,20 +3759,20 @@
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>3VbCMl1_928hbAKPG5Knzl</t>
+          <t>1QH5Axl111J9SJj2E3W4vx</t>
         </is>
       </c>
       <c r="CE14" t="n">
-        <v>4.121</v>
+        <v>3.42000304025274</v>
       </c>
       <c r="CF14" t="n">
-        <v>20.2968268134622</v>
+        <v>26.887076979177</v>
       </c>
       <c r="CG14" t="n">
-        <v>10.7493655</v>
+        <v>18.0784765</v>
       </c>
       <c r="CH14" t="n">
-        <v>44.2981352255</v>
+        <v>61.8284445931377</v>
       </c>
       <c r="CI14" t="inlineStr">
         <is>
@@ -3792,10 +3792,10 @@
         </is>
       </c>
       <c r="CR14" t="n">
-        <v>10.7493655</v>
+        <v>0</v>
       </c>
       <c r="CS14" t="n">
-        <v>0</v>
+        <v>18.0784765</v>
       </c>
       <c r="CT14" t="n">
         <v>0</v>
@@ -3812,14 +3812,14 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>1228</v>
+        <v>1204</v>
       </c>
       <c r="B15" t="n">
-        <v>1208</v>
+        <v>1187</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2g6H0ojnvDdueYpZ_5Zux8</t>
+          <t>1jaqyoTjT5Bhtkj1U9RyUu</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3839,11 +3839,11 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>KOR:342423</t>
+          <t>KOR:343102</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>1228</v>
+        <v>1204</v>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
@@ -3871,11 +3871,11 @@
       <c r="AB15" t="inlineStr"/>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>UG1</t>
+          <t>OG2</t>
         </is>
       </c>
       <c r="AD15" t="n">
-        <v>-3.78</v>
+        <v>7.94</v>
       </c>
       <c r="AE15" t="inlineStr"/>
       <c r="AF15" t="inlineStr"/>
@@ -3982,20 +3982,20 @@
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>1QH5Axl111J9SJj2E3W4vx</t>
+          <t>0b93QOWH141xpbKCpGEr9v</t>
         </is>
       </c>
       <c r="CE15" t="n">
-        <v>3.421</v>
+        <v>3.57800180084113</v>
       </c>
       <c r="CF15" t="n">
-        <v>26.887076979177</v>
+        <v>22.2995095258837</v>
       </c>
       <c r="CG15" t="n">
-        <v>18.0784765</v>
+        <v>13.6486625</v>
       </c>
       <c r="CH15" t="n">
-        <v>61.8464681065</v>
+        <v>48.8349390040728</v>
       </c>
       <c r="CI15" t="inlineStr">
         <is>
@@ -4018,7 +4018,7 @@
         <v>0</v>
       </c>
       <c r="CS15" t="n">
-        <v>18.0784765</v>
+        <v>0</v>
       </c>
       <c r="CT15" t="n">
         <v>0</v>
@@ -4027,7 +4027,7 @@
         <v>0</v>
       </c>
       <c r="CV15" t="n">
-        <v>0</v>
+        <v>13.6486625</v>
       </c>
       <c r="CW15" t="n">
         <v>0</v>
@@ -4035,14 +4035,14 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>1229</v>
+        <v>1205</v>
       </c>
       <c r="B16" t="n">
-        <v>1211</v>
+        <v>1188</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>1rOBySJhH5b9YWwDU_guK1</t>
+          <t>3yI4yvxYX9aBv$Jk3GB$dy</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -4062,11 +4062,11 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>KOR:343102</t>
+          <t>KOR:343282</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>1229</v>
+        <v>1205</v>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
@@ -4094,11 +4094,11 @@
       <c r="AB16" t="inlineStr"/>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>OG2</t>
+          <t>OG3</t>
         </is>
       </c>
       <c r="AD16" t="n">
-        <v>7.939</v>
+        <v>11.948</v>
       </c>
       <c r="AE16" t="inlineStr"/>
       <c r="AF16" t="inlineStr"/>
@@ -4205,20 +4205,20 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>0b93QOWH141xpbKCpGEr9v</t>
+          <t>3ol_0stLL7q8pSNseENpkf</t>
         </is>
       </c>
       <c r="CE16" t="n">
-        <v>3.579</v>
+        <v>2.522</v>
       </c>
       <c r="CF16" t="n">
-        <v>22.2995095258837</v>
+        <v>24.6411125862649</v>
       </c>
       <c r="CG16" t="n">
-        <v>13.6486625</v>
+        <v>13.547317</v>
       </c>
       <c r="CH16" t="n">
-        <v>48.8485630875</v>
+        <v>34.166333474</v>
       </c>
       <c r="CI16" t="inlineStr">
         <is>
@@ -4250,22 +4250,22 @@
         <v>0</v>
       </c>
       <c r="CV16" t="n">
-        <v>13.6486625</v>
+        <v>0</v>
       </c>
       <c r="CW16" t="n">
-        <v>0</v>
+        <v>13.547317</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>1230</v>
+        <v>1206</v>
       </c>
       <c r="B17" t="n">
-        <v>1209</v>
+        <v>1185</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>3vSADXkCf9CehgpLlu0Bds</t>
+          <t>367VhQ1U19B8v9mWQKmOzz</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -4285,11 +4285,11 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>UUF:343913</t>
+          <t>UUF:343919</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>1230</v>
+        <v>1206</v>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
@@ -4428,20 +4428,20 @@
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>3qJ9B5zvT7$hh913fcAFEG</t>
+          <t>3qJ9B5zvT7$hh913fcAFEM</t>
         </is>
       </c>
       <c r="CE17" t="n">
         <v>1</v>
       </c>
       <c r="CF17" t="n">
-        <v>28.3650362774305</v>
+        <v>27.1053636632595</v>
       </c>
       <c r="CG17" t="n">
-        <v>13.032036</v>
+        <v>35.456544</v>
       </c>
       <c r="CH17" t="n">
-        <v>13.032036</v>
+        <v>35.456544</v>
       </c>
       <c r="CI17" t="inlineStr">
         <is>
@@ -4471,7 +4471,7 @@
         <v>0</v>
       </c>
       <c r="CT17" t="n">
-        <v>13.032036</v>
+        <v>35.456544</v>
       </c>
       <c r="CU17" t="n">
         <v>0</v>
@@ -4485,14 +4485,14 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>1231</v>
+        <v>1207</v>
       </c>
       <c r="B18" t="n">
-        <v>1209</v>
+        <v>1185</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2vZ$D3URf34vJnBMMHx9xX</t>
+          <t>2Hxz6DXsT92vehhFG6_ShJ</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -4512,11 +4512,11 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>UUF:343919</t>
+          <t>UUF:344049</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>1231</v>
+        <v>1207</v>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
@@ -4655,20 +4655,20 @@
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>3qJ9B5zvT7$hh913fcAFEM</t>
+          <t>3qJ9B5zvT7$hh913fcAFC8</t>
         </is>
       </c>
       <c r="CE18" t="n">
         <v>1</v>
       </c>
       <c r="CF18" t="n">
-        <v>27.1971243796257</v>
+        <v>164.979919618776</v>
       </c>
       <c r="CG18" t="n">
-        <v>35.7954435</v>
+        <v>259.062335</v>
       </c>
       <c r="CH18" t="n">
-        <v>35.7954435</v>
+        <v>259.062335</v>
       </c>
       <c r="CI18" t="inlineStr">
         <is>
@@ -4698,7 +4698,7 @@
         <v>0</v>
       </c>
       <c r="CT18" t="n">
-        <v>35.7954435</v>
+        <v>259.062335</v>
       </c>
       <c r="CU18" t="n">
         <v>0</v>
@@ -4712,14 +4712,14 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>1232</v>
+        <v>1208</v>
       </c>
       <c r="B19" t="n">
-        <v>1209</v>
+        <v>1185</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>1D6v$lAcHDiAsIdGYCYrg4</t>
+          <t>38tAZDumv6$hnRXN0FwtYj</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4739,11 +4739,11 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>UUF:344049</t>
+          <t>UUF:344052</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>1232</v>
+        <v>1208</v>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
@@ -4882,20 +4882,20 @@
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>3qJ9B5zvT7$hh913fcAFC8</t>
+          <t>3qJ9B5zvT7$hh913fcAFCD</t>
         </is>
       </c>
       <c r="CE19" t="n">
         <v>1</v>
       </c>
       <c r="CF19" t="n">
-        <v>165.175783539062</v>
+        <v>32.1979140750708</v>
       </c>
       <c r="CG19" t="n">
-        <v>258.794827</v>
+        <v>56.537983</v>
       </c>
       <c r="CH19" t="n">
-        <v>258.794827</v>
+        <v>56.537983</v>
       </c>
       <c r="CI19" t="inlineStr">
         <is>
@@ -4925,7 +4925,7 @@
         <v>0</v>
       </c>
       <c r="CT19" t="n">
-        <v>258.794827</v>
+        <v>56.537983</v>
       </c>
       <c r="CU19" t="n">
         <v>0</v>
@@ -4939,38 +4939,38 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>1233</v>
+        <v>1209</v>
       </c>
       <c r="B20" t="n">
+        <v>1184</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>3W2HgVPjj8sgJOb9kc$BUn</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>IfcSpace</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>VRF:342387</t>
+        </is>
+      </c>
+      <c r="H20" t="n">
         <v>1209</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>14Y66SGP5Fm8iYaOLsp2V8</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>IfcSpace</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>UUF:344052</t>
-        </is>
-      </c>
-      <c r="H20" t="n">
-        <v>1233</v>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
@@ -4985,7 +4985,7 @@
       <c r="S20" t="inlineStr"/>
       <c r="T20" t="inlineStr">
         <is>
-          <t>EXTERNAL</t>
+          <t>INTERNAL</t>
         </is>
       </c>
       <c r="U20" t="inlineStr"/>
@@ -4998,11 +4998,11 @@
       <c r="AB20" t="inlineStr"/>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>EG</t>
+          <t>UG1</t>
         </is>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>-3.78</v>
       </c>
       <c r="AE20" t="inlineStr"/>
       <c r="AF20" t="inlineStr"/>
@@ -5058,41 +5058,41 @@
       <c r="BR20" t="inlineStr"/>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>UUF</t>
+          <t>VRF</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
         <is>
-          <t>Aussenbereich</t>
+          <t>Allgemein</t>
         </is>
       </c>
       <c r="BU20" t="inlineStr">
         <is>
-          <t>Aussenanlagen</t>
+          <t>Allgemein</t>
         </is>
       </c>
       <c r="BV20" t="inlineStr">
         <is>
-          <t>Unbearbeitete Umgebungsflächen</t>
+          <t>Verkehrsfläche</t>
         </is>
       </c>
       <c r="BW20" t="inlineStr">
         <is>
-          <t>Alle restlichen unbearbeiteten Aussenanlagenflächen bis zur Grundstücksgrenze</t>
+          <t>nach Bedarf</t>
         </is>
       </c>
       <c r="BX20" t="inlineStr">
         <is>
-          <t>UUF  -  Unbearbeitete Umgebungsflächen</t>
+          <t>VRF  -  Verkehrsfläche</t>
         </is>
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>EXTERNAL</t>
+          <t>INTERNAL</t>
         </is>
       </c>
       <c r="BZ20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CA20" t="n">
         <v>1</v>
@@ -5109,31 +5109,27 @@
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>3qJ9B5zvT7$hh913fcAFCD</t>
+          <t>1QH5Axl111J9SJj2E3W4wV</t>
         </is>
       </c>
       <c r="CE20" t="n">
-        <v>1</v>
+        <v>3.42</v>
       </c>
       <c r="CF20" t="n">
-        <v>32.1979140750708</v>
+        <v>63.7340745259235</v>
       </c>
       <c r="CG20" t="n">
-        <v>56.537983</v>
+        <v>49.7657485</v>
       </c>
       <c r="CH20" t="n">
-        <v>56.537983</v>
+        <v>170.19885987</v>
       </c>
       <c r="CI20" t="inlineStr">
         <is>
-          <t>BUF</t>
-        </is>
-      </c>
-      <c r="CJ20" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
+          <t>VF</t>
+        </is>
+      </c>
+      <c r="CJ20" t="inlineStr"/>
       <c r="CK20" t="inlineStr"/>
       <c r="CL20" t="inlineStr"/>
       <c r="CM20" t="inlineStr"/>
@@ -5142,17 +5138,17 @@
       <c r="CP20" t="inlineStr"/>
       <c r="CQ20" t="inlineStr">
         <is>
-          <t>Aussenbereich_UUF</t>
+          <t>Allgemein_VRF</t>
         </is>
       </c>
       <c r="CR20" t="n">
         <v>0</v>
       </c>
       <c r="CS20" t="n">
-        <v>0</v>
+        <v>49.7657485</v>
       </c>
       <c r="CT20" t="n">
-        <v>56.537983</v>
+        <v>0</v>
       </c>
       <c r="CU20" t="n">
         <v>0</v>
@@ -5166,14 +5162,14 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>1234</v>
+        <v>1210</v>
       </c>
       <c r="B21" t="n">
-        <v>1208</v>
+        <v>1184</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>14zTAK7eDFxu25AGckILdY</t>
+          <t>3W8P9$rMX2_fA9sfb6fwqp</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -5193,11 +5189,11 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>VRF:342387</t>
+          <t>VRF:342402</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>1234</v>
+        <v>1210</v>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
@@ -5336,20 +5332,20 @@
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>1QH5Axl111J9SJj2E3W4wV</t>
+          <t>1QH5Axl111J9SJj2E3W4vk</t>
         </is>
       </c>
       <c r="CE21" t="n">
-        <v>3.421</v>
+        <v>3.42</v>
       </c>
       <c r="CF21" t="n">
-        <v>64.01776445924619</v>
+        <v>8.247282695482101</v>
       </c>
       <c r="CG21" t="n">
-        <v>50.4801045</v>
+        <v>4.2125125</v>
       </c>
       <c r="CH21" t="n">
-        <v>172.6924374945</v>
+        <v>14.40679275</v>
       </c>
       <c r="CI21" t="inlineStr">
         <is>
@@ -5372,7 +5368,7 @@
         <v>0</v>
       </c>
       <c r="CS21" t="n">
-        <v>50.4801045</v>
+        <v>4.2125125</v>
       </c>
       <c r="CT21" t="n">
         <v>0</v>
@@ -5389,14 +5385,14 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>1235</v>
+        <v>1211</v>
       </c>
       <c r="B22" t="n">
-        <v>1208</v>
+        <v>1185</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>3_49$ldkHAGOZei44e_8FY</t>
+          <t>0HX_qt1yzF3xKWplASPhYe</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -5416,11 +5412,11 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>VRF:342402</t>
+          <t>BUF:345808</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>1235</v>
+        <v>1211</v>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
@@ -5435,7 +5431,7 @@
       <c r="S22" t="inlineStr"/>
       <c r="T22" t="inlineStr">
         <is>
-          <t>INTERNAL</t>
+          <t>EXTERNAL</t>
         </is>
       </c>
       <c r="U22" t="inlineStr"/>
@@ -5448,11 +5444,11 @@
       <c r="AB22" t="inlineStr"/>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>UG1</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="AD22" t="n">
-        <v>-3.78</v>
+        <v>0</v>
       </c>
       <c r="AE22" t="inlineStr"/>
       <c r="AF22" t="inlineStr"/>
@@ -5508,41 +5504,41 @@
       <c r="BR22" t="inlineStr"/>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>VRF</t>
+          <t>BUF</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
         <is>
-          <t>Allgemein</t>
+          <t>Aussenbereich</t>
         </is>
       </c>
       <c r="BU22" t="inlineStr">
         <is>
-          <t>Allgemein</t>
+          <t>Aussenanlagen</t>
         </is>
       </c>
       <c r="BV22" t="inlineStr">
         <is>
-          <t>Verkehrsfläche</t>
+          <t>Bearbeitet Umgebungsflächen</t>
         </is>
       </c>
       <c r="BW22" t="inlineStr">
         <is>
-          <t>nach Bedarf</t>
+          <t>Alle restlichen bearbeiteten Aussenanlagenflächen bis zur Grundstücksgrenze</t>
         </is>
       </c>
       <c r="BX22" t="inlineStr">
         <is>
-          <t>VRF  -  Verkehrsfläche</t>
+          <t>BUF  -  Bearbeitet Umgebungsflächen</t>
         </is>
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>INTERNAL</t>
+          <t>EXTERNAL</t>
         </is>
       </c>
       <c r="BZ22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CA22" t="n">
         <v>1</v>
@@ -5559,27 +5555,31 @@
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>1QH5Axl111J9SJj2E3W4vk</t>
+          <t>3EjVH2xK16fxVS2$WCt57y</t>
         </is>
       </c>
       <c r="CE22" t="n">
-        <v>3.421</v>
+        <v>1</v>
       </c>
       <c r="CF22" t="n">
-        <v>8.247282695482101</v>
+        <v>93.1053783306551</v>
       </c>
       <c r="CG22" t="n">
-        <v>4.2125125</v>
+        <v>330.8825295</v>
       </c>
       <c r="CH22" t="n">
-        <v>14.4110052625</v>
+        <v>330.8825295</v>
       </c>
       <c r="CI22" t="inlineStr">
         <is>
-          <t>VF</t>
-        </is>
-      </c>
-      <c r="CJ22" t="inlineStr"/>
+          <t>BUF</t>
+        </is>
+      </c>
+      <c r="CJ22" t="inlineStr">
+        <is>
+          <t>???</t>
+        </is>
+      </c>
       <c r="CK22" t="inlineStr"/>
       <c r="CL22" t="inlineStr"/>
       <c r="CM22" t="inlineStr"/>
@@ -5588,17 +5588,17 @@
       <c r="CP22" t="inlineStr"/>
       <c r="CQ22" t="inlineStr">
         <is>
-          <t>Allgemein_VRF</t>
+          <t>Aussenbereich_BUF</t>
         </is>
       </c>
       <c r="CR22" t="n">
         <v>0</v>
       </c>
       <c r="CS22" t="n">
-        <v>4.2125125</v>
+        <v>0</v>
       </c>
       <c r="CT22" t="n">
-        <v>0</v>
+        <v>330.8825295</v>
       </c>
       <c r="CU22" t="n">
         <v>0</v>
@@ -5612,14 +5612,14 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>1236</v>
+        <v>1212</v>
       </c>
       <c r="B23" t="n">
-        <v>1209</v>
+        <v>1188</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2smUqi2i10zRE_diOVjJhu</t>
+          <t>2qXFUIy2T3SBxq9lBM4xHo</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -5639,11 +5639,11 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>BUF:345808</t>
+          <t>BUF:345410</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>1236</v>
+        <v>1212</v>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
@@ -5671,11 +5671,11 @@
       <c r="AB23" t="inlineStr"/>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>EG</t>
+          <t>OG3</t>
         </is>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>11.948</v>
       </c>
       <c r="AE23" t="inlineStr"/>
       <c r="AF23" t="inlineStr"/>
@@ -5782,20 +5782,20 @@
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>3EjVH2xK16fxVS2$WCt57y</t>
+          <t>2VFBkNPLX5hxPkFzLFhskz</t>
         </is>
       </c>
       <c r="CE23" t="n">
         <v>1</v>
       </c>
       <c r="CF23" t="n">
-        <v>93.1053783306551</v>
+        <v>26.6601989972909</v>
       </c>
       <c r="CG23" t="n">
-        <v>330.8825295</v>
+        <v>29.3330605</v>
       </c>
       <c r="CH23" t="n">
-        <v>330.8825295</v>
+        <v>29.3330605</v>
       </c>
       <c r="CI23" t="inlineStr">
         <is>
@@ -5825,7 +5825,7 @@
         <v>0</v>
       </c>
       <c r="CT23" t="n">
-        <v>330.8825295</v>
+        <v>0</v>
       </c>
       <c r="CU23" t="n">
         <v>0</v>
@@ -5834,19 +5834,19 @@
         <v>0</v>
       </c>
       <c r="CW23" t="n">
-        <v>0</v>
+        <v>29.3330605</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>1237</v>
+        <v>1213</v>
       </c>
       <c r="B24" t="n">
-        <v>1212</v>
+        <v>1188</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2VPJztHKzE5eU2jmaJhVnb</t>
+          <t>2RrGEvz4H6O8oYwW_ERzQ6</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5866,11 +5866,11 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>BUF:345410</t>
+          <t>BUF:345413</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>1237</v>
+        <v>1213</v>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
@@ -5902,7 +5902,7 @@
         </is>
       </c>
       <c r="AD24" t="n">
-        <v>11.947</v>
+        <v>11.948</v>
       </c>
       <c r="AE24" t="inlineStr"/>
       <c r="AF24" t="inlineStr"/>
@@ -6009,20 +6009,20 @@
       </c>
       <c r="CD24" t="inlineStr">
         <is>
-          <t>2VFBkNPLX5hxPkFzLFhskz</t>
+          <t>2VFBkNPLX5hxPkFzLFhskw</t>
         </is>
       </c>
       <c r="CE24" t="n">
-        <v>1.001</v>
+        <v>1</v>
       </c>
       <c r="CF24" t="n">
-        <v>26.6148846931745</v>
+        <v>25.0995479191626</v>
       </c>
       <c r="CG24" t="n">
-        <v>29.418831</v>
+        <v>49.998075</v>
       </c>
       <c r="CH24" t="n">
-        <v>29.448249831</v>
+        <v>49.998075</v>
       </c>
       <c r="CI24" t="inlineStr">
         <is>
@@ -6061,19 +6061,19 @@
         <v>0</v>
       </c>
       <c r="CW24" t="n">
-        <v>29.418831</v>
+        <v>49.998075</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>1238</v>
+        <v>1214</v>
       </c>
       <c r="B25" t="n">
-        <v>1212</v>
+        <v>1188</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>360G1aSpvFCuurfPO7oVVK</t>
+          <t>1AENlAVbf0FPNqAceD_OOg</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -6093,11 +6093,11 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>BUF:345413</t>
+          <t>BUF:345445</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>1238</v>
+        <v>1214</v>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
@@ -6129,7 +6129,7 @@
         </is>
       </c>
       <c r="AD25" t="n">
-        <v>11.947</v>
+        <v>11.948</v>
       </c>
       <c r="AE25" t="inlineStr"/>
       <c r="AF25" t="inlineStr"/>
@@ -6236,20 +6236,20 @@
       </c>
       <c r="CD25" t="inlineStr">
         <is>
-          <t>2VFBkNPLX5hxPkFzLFhskw</t>
+          <t>2VFBkNPLX5hxPkFzLFhskQ</t>
         </is>
       </c>
       <c r="CE25" t="n">
-        <v>1.001</v>
+        <v>0.9980058549395801</v>
       </c>
       <c r="CF25" t="n">
-        <v>22.6274169979695</v>
+        <v>26.6595601224005</v>
       </c>
       <c r="CG25" t="n">
-        <v>32</v>
+        <v>29.3323215</v>
       </c>
       <c r="CH25" t="n">
-        <v>32.032</v>
+        <v>29.2738285959701</v>
       </c>
       <c r="CI25" t="inlineStr">
         <is>
@@ -6288,19 +6288,19 @@
         <v>0</v>
       </c>
       <c r="CW25" t="n">
-        <v>32</v>
+        <v>29.3323215</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>1239</v>
+        <v>1215</v>
       </c>
       <c r="B26" t="n">
-        <v>1212</v>
+        <v>1185</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2gK95MKEPE$O83dwER37Qp</t>
+          <t>2vghzoGT51TxNQvOAAv0j4</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -6320,11 +6320,11 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>BUF:345445</t>
+          <t>UUF:343895</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>1239</v>
+        <v>1215</v>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
@@ -6352,11 +6352,11 @@
       <c r="AB26" t="inlineStr"/>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>OG3</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="AD26" t="n">
-        <v>11.947</v>
+        <v>0</v>
       </c>
       <c r="AE26" t="inlineStr"/>
       <c r="AF26" t="inlineStr"/>
@@ -6412,7 +6412,7 @@
       <c r="BR26" t="inlineStr"/>
       <c r="BS26" t="inlineStr">
         <is>
-          <t>BUF</t>
+          <t>UUF</t>
         </is>
       </c>
       <c r="BT26" t="inlineStr">
@@ -6427,17 +6427,17 @@
       </c>
       <c r="BV26" t="inlineStr">
         <is>
-          <t>Bearbeitet Umgebungsflächen</t>
+          <t>Unbearbeitete Umgebungsflächen</t>
         </is>
       </c>
       <c r="BW26" t="inlineStr">
         <is>
-          <t>Alle restlichen bearbeiteten Aussenanlagenflächen bis zur Grundstücksgrenze</t>
+          <t>Alle restlichen unbearbeiteten Aussenanlagenflächen bis zur Grundstücksgrenze</t>
         </is>
       </c>
       <c r="BX26" t="inlineStr">
         <is>
-          <t>BUF  -  Bearbeitet Umgebungsflächen</t>
+          <t>UUF  -  Unbearbeitete Umgebungsflächen</t>
         </is>
       </c>
       <c r="BY26" t="inlineStr">
@@ -6463,20 +6463,20 @@
       </c>
       <c r="CD26" t="inlineStr">
         <is>
-          <t>2VFBkNPLX5hxPkFzLFhskQ</t>
+          <t>3qJ9B5zvT7$hh913fcAFEk</t>
         </is>
       </c>
       <c r="CE26" t="n">
-        <v>1.001</v>
+        <v>1.00001926331646</v>
       </c>
       <c r="CF26" t="n">
-        <v>26.6132231953422</v>
+        <v>71.8572432719856</v>
       </c>
       <c r="CG26" t="n">
-        <v>29.4185435</v>
+        <v>24.9312215</v>
       </c>
       <c r="CH26" t="n">
-        <v>29.4479620435</v>
+        <v>24.9317017580095</v>
       </c>
       <c r="CI26" t="inlineStr">
         <is>
@@ -6485,7 +6485,7 @@
       </c>
       <c r="CJ26" t="inlineStr">
         <is>
-          <t>???</t>
+          <t>true</t>
         </is>
       </c>
       <c r="CK26" t="inlineStr"/>
@@ -6496,7 +6496,7 @@
       <c r="CP26" t="inlineStr"/>
       <c r="CQ26" t="inlineStr">
         <is>
-          <t>Aussenbereich_BUF</t>
+          <t>Aussenbereich_UUF</t>
         </is>
       </c>
       <c r="CR26" t="n">
@@ -6506,7 +6506,7 @@
         <v>0</v>
       </c>
       <c r="CT26" t="n">
-        <v>0</v>
+        <v>24.9312215</v>
       </c>
       <c r="CU26" t="n">
         <v>0</v>
@@ -6515,19 +6515,19 @@
         <v>0</v>
       </c>
       <c r="CW26" t="n">
-        <v>29.4185435</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>1240</v>
+        <v>1216</v>
       </c>
       <c r="B27" t="n">
-        <v>1209</v>
+        <v>1185</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>0XbzWrb4P70RH_r69FZvNC</t>
+          <t>2rIGmJBcz82eOKIU2HIoRF</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -6547,11 +6547,11 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>UUF:343895</t>
+          <t>UUF:343913</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>1240</v>
+        <v>1216</v>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
@@ -6690,20 +6690,20 @@
       </c>
       <c r="CD27" t="inlineStr">
         <is>
-          <t>3qJ9B5zvT7$hh913fcAFEk</t>
+          <t>3qJ9B5zvT7$hh913fcAFEG</t>
         </is>
       </c>
       <c r="CE27" t="n">
         <v>1</v>
       </c>
       <c r="CF27" t="n">
-        <v>71.8572432719856</v>
+        <v>28.8364393051884</v>
       </c>
       <c r="CG27" t="n">
-        <v>24.9312215</v>
+        <v>13.119374</v>
       </c>
       <c r="CH27" t="n">
-        <v>24.9312215</v>
+        <v>13.119374</v>
       </c>
       <c r="CI27" t="inlineStr">
         <is>
@@ -6733,7 +6733,7 @@
         <v>0</v>
       </c>
       <c r="CT27" t="n">
-        <v>24.9312215</v>
+        <v>13.119374</v>
       </c>
       <c r="CU27" t="n">
         <v>0</v>
@@ -6747,14 +6747,14 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>1241</v>
+        <v>1217</v>
       </c>
       <c r="B28" t="n">
-        <v>1209</v>
+        <v>1185</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>0WtOOP9cn9MBUnf0AHUQfJ</t>
+          <t>0eDs_7T5r34RBessIb8ALy</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -6778,7 +6778,7 @@
         </is>
       </c>
       <c r="H28" t="n">
-        <v>1241</v>
+        <v>1217</v>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr"/>
@@ -6974,14 +6974,14 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>1242</v>
+        <v>1218</v>
       </c>
       <c r="B29" t="n">
-        <v>1209</v>
+        <v>1185</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2u0jNhx4PBahQiA_Mn0fAT</t>
+          <t>2KTKdUnXz3EAT3eZQsBIVW</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -7005,7 +7005,7 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>1242</v>
+        <v>1218</v>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr"/>
@@ -7201,14 +7201,14 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>1243</v>
+        <v>1219</v>
       </c>
       <c r="B30" t="n">
-        <v>1209</v>
+        <v>1185</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>1XvgrEk2L7Sf0_v9d5iT66</t>
+          <t>1dm6hXA1TAHxySfbOH_SuE</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -7232,7 +7232,7 @@
         </is>
       </c>
       <c r="H30" t="n">
-        <v>1243</v>
+        <v>1219</v>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr"/>
@@ -7428,14 +7428,14 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>1244</v>
+        <v>1220</v>
       </c>
       <c r="B31" t="n">
-        <v>1209</v>
+        <v>1185</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>02z0dETOLCdvSjB6spGLDD</t>
+          <t>3Ko5GwjxPFa8wWHDHgsYet</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -7459,7 +7459,7 @@
         </is>
       </c>
       <c r="H31" t="n">
-        <v>1244</v>
+        <v>1220</v>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr"/>
@@ -7655,14 +7655,14 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>1245</v>
+        <v>1221</v>
       </c>
       <c r="B32" t="n">
-        <v>1209</v>
+        <v>1185</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>2dWGfk8A5FP9hGnKCxZb2t</t>
+          <t>0bj3cexLz16A$8LPJ5vRgB</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -7686,7 +7686,7 @@
         </is>
       </c>
       <c r="H32" t="n">
-        <v>1245</v>
+        <v>1221</v>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr"/>
@@ -7882,14 +7882,14 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>1246</v>
+        <v>1222</v>
       </c>
       <c r="B33" t="n">
-        <v>1209</v>
+        <v>1185</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>1MqvEZmU539xzlBdmFG0Gt</t>
+          <t>3Zzx4L78nBqBHz3ZA4ivSQ</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -7909,11 +7909,11 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>VEL_L:343934</t>
+          <t>VEL_S:343931</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>1246</v>
+        <v>1222</v>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr"/>
@@ -8001,7 +8001,7 @@
       <c r="BR33" t="inlineStr"/>
       <c r="BS33" t="inlineStr">
         <is>
-          <t>VEL_L</t>
+          <t>VEL_S</t>
         </is>
       </c>
       <c r="BT33" t="inlineStr">
@@ -8016,17 +8016,17 @@
       </c>
       <c r="BV33" t="inlineStr">
         <is>
-          <t>Velo- Abstellplätze Schulpersonal</t>
+          <t>Velo- Abstellplätze Schulkinder</t>
         </is>
       </c>
       <c r="BW33" t="inlineStr">
         <is>
-          <t>8 Stück, Gedeckt und gegen Diebstahl und Vanalismus geschützt</t>
+          <t>13 Stück, davon mind 1/3 überdacht, idealerweise alle</t>
         </is>
       </c>
       <c r="BX33" t="inlineStr">
         <is>
-          <t>VEL_L  -  Velo- Abstellplätze Schulpersonal</t>
+          <t>VEL_S  -  Velo- Abstellplätze Schulkinder</t>
         </is>
       </c>
       <c r="BY33" t="inlineStr">
@@ -8052,20 +8052,20 @@
       </c>
       <c r="CD33" t="inlineStr">
         <is>
-          <t>3qJ9B5zvT7$hh913fcAFE7</t>
+          <t>3qJ9B5zvT7$hh913fcAFE2</t>
         </is>
       </c>
       <c r="CE33" t="n">
-        <v>1</v>
+        <v>0.999999999999999</v>
       </c>
       <c r="CF33" t="n">
-        <v>9.201563573455161</v>
+        <v>22.2049630491981</v>
       </c>
       <c r="CG33" t="n">
-        <v>5.20168</v>
+        <v>18.206341</v>
       </c>
       <c r="CH33" t="n">
-        <v>5.20168</v>
+        <v>18.206341</v>
       </c>
       <c r="CI33" t="inlineStr">
         <is>
@@ -8087,7 +8087,7 @@
       <c r="CP33" t="inlineStr"/>
       <c r="CQ33" t="inlineStr">
         <is>
-          <t>Aussenbereich_VEL_L</t>
+          <t>Aussenbereich_VEL_S</t>
         </is>
       </c>
       <c r="CR33" t="n">
@@ -8097,7 +8097,7 @@
         <v>0</v>
       </c>
       <c r="CT33" t="n">
-        <v>5.20168</v>
+        <v>18.206341</v>
       </c>
       <c r="CU33" t="n">
         <v>0</v>
@@ -8111,14 +8111,14 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>1247</v>
+        <v>1223</v>
       </c>
       <c r="B34" t="n">
-        <v>1209</v>
+        <v>1185</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>3eJReeN3j08hoB6uk90Meh</t>
+          <t>0wQhe8bif1LOoZtbl2gXny</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -8138,11 +8138,11 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>VEL_S:343931</t>
+          <t>AVF:343904</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>1247</v>
+        <v>1223</v>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr"/>
@@ -8230,7 +8230,7 @@
       <c r="BR34" t="inlineStr"/>
       <c r="BS34" t="inlineStr">
         <is>
-          <t>VEL_S</t>
+          <t>AVF</t>
         </is>
       </c>
       <c r="BT34" t="inlineStr">
@@ -8245,17 +8245,17 @@
       </c>
       <c r="BV34" t="inlineStr">
         <is>
-          <t>Velo- Abstellplätze Schulkinder</t>
+          <t>Zufahrt, Abstandsfläche, Umschwung</t>
         </is>
       </c>
       <c r="BW34" t="inlineStr">
         <is>
-          <t>13 Stück, davon mind 1/3 überdacht, idealerweise alle</t>
+          <t>nach Bedarf</t>
         </is>
       </c>
       <c r="BX34" t="inlineStr">
         <is>
-          <t>VEL_S  -  Velo- Abstellplätze Schulkinder</t>
+          <t>AVF  -  Zufahrt, Abstandsfläche, Umschwung</t>
         </is>
       </c>
       <c r="BY34" t="inlineStr">
@@ -8281,20 +8281,20 @@
       </c>
       <c r="CD34" t="inlineStr">
         <is>
-          <t>3qJ9B5zvT7$hh913fcAFE2</t>
+          <t>3qJ9B5zvT7$hh913fcAFEP</t>
         </is>
       </c>
       <c r="CE34" t="n">
-        <v>0.999999999999999</v>
+        <v>1</v>
       </c>
       <c r="CF34" t="n">
-        <v>22.2049630491981</v>
+        <v>14.5215458021443</v>
       </c>
       <c r="CG34" t="n">
-        <v>18.206341</v>
+        <v>12.9937485</v>
       </c>
       <c r="CH34" t="n">
-        <v>18.206341</v>
+        <v>12.9937485</v>
       </c>
       <c r="CI34" t="inlineStr">
         <is>
@@ -8306,9 +8306,7 @@
           <t>false</t>
         </is>
       </c>
-      <c r="CK34" t="n">
-        <v>10.1</v>
-      </c>
+      <c r="CK34" t="inlineStr"/>
       <c r="CL34" t="inlineStr"/>
       <c r="CM34" t="inlineStr"/>
       <c r="CN34" t="inlineStr"/>
@@ -8316,7 +8314,7 @@
       <c r="CP34" t="inlineStr"/>
       <c r="CQ34" t="inlineStr">
         <is>
-          <t>Aussenbereich_VEL_S</t>
+          <t>Aussenbereich_AVF</t>
         </is>
       </c>
       <c r="CR34" t="n">
@@ -8326,7 +8324,7 @@
         <v>0</v>
       </c>
       <c r="CT34" t="n">
-        <v>18.206341</v>
+        <v>12.9937485</v>
       </c>
       <c r="CU34" t="n">
         <v>0</v>
@@ -8340,14 +8338,14 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>1248</v>
+        <v>1224</v>
       </c>
       <c r="B35" t="n">
-        <v>1209</v>
+        <v>1185</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>3OwC$bqnH8HPMox51VeeVy</t>
+          <t>2CKlKmb3L8if01dRSHZkQk</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -8367,11 +8365,11 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>AVF:343904</t>
+          <t>BUF:343892</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>1248</v>
+        <v>1224</v>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr"/>
@@ -8459,7 +8457,7 @@
       <c r="BR35" t="inlineStr"/>
       <c r="BS35" t="inlineStr">
         <is>
-          <t>AVF</t>
+          <t>BUF</t>
         </is>
       </c>
       <c r="BT35" t="inlineStr">
@@ -8474,17 +8472,17 @@
       </c>
       <c r="BV35" t="inlineStr">
         <is>
-          <t>Zufahrt, Abstandsfläche, Umschwung</t>
+          <t>Bearbeitet Umgebungsflächen</t>
         </is>
       </c>
       <c r="BW35" t="inlineStr">
         <is>
-          <t>nach Bedarf</t>
+          <t>Alle restlichen bearbeiteten Aussenanlagenflächen bis zur Grundstücksgrenze</t>
         </is>
       </c>
       <c r="BX35" t="inlineStr">
         <is>
-          <t>AVF  -  Zufahrt, Abstandsfläche, Umschwung</t>
+          <t>BUF  -  Bearbeitet Umgebungsflächen</t>
         </is>
       </c>
       <c r="BY35" t="inlineStr">
@@ -8510,20 +8508,20 @@
       </c>
       <c r="CD35" t="inlineStr">
         <is>
-          <t>3qJ9B5zvT7$hh913fcAFEP</t>
+          <t>3qJ9B5zvT7$hh913fcAFEj</t>
         </is>
       </c>
       <c r="CE35" t="n">
-        <v>1</v>
+        <v>1.00002454702819</v>
       </c>
       <c r="CF35" t="n">
-        <v>14.5215458021443</v>
+        <v>118.873554291617</v>
       </c>
       <c r="CG35" t="n">
-        <v>12.9937485</v>
+        <v>162.490801</v>
       </c>
       <c r="CH35" t="n">
-        <v>12.9937485</v>
+        <v>162.494789666272</v>
       </c>
       <c r="CI35" t="inlineStr">
         <is>
@@ -8532,7 +8530,7 @@
       </c>
       <c r="CJ35" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>???</t>
         </is>
       </c>
       <c r="CK35" t="inlineStr"/>
@@ -8543,7 +8541,7 @@
       <c r="CP35" t="inlineStr"/>
       <c r="CQ35" t="inlineStr">
         <is>
-          <t>Aussenbereich_AVF</t>
+          <t>Aussenbereich_BUF</t>
         </is>
       </c>
       <c r="CR35" t="n">
@@ -8553,7 +8551,7 @@
         <v>0</v>
       </c>
       <c r="CT35" t="n">
-        <v>12.9937485</v>
+        <v>162.490801</v>
       </c>
       <c r="CU35" t="n">
         <v>0</v>
@@ -8567,14 +8565,14 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>1249</v>
+        <v>1225</v>
       </c>
       <c r="B36" t="n">
-        <v>1209</v>
+        <v>1185</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>3Dk2HhiCr35RYXuSaVOvs6</t>
+          <t>3VSDX0a6j5R9Sc3ExLWrsf</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -8594,11 +8592,11 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>BUF:343892</t>
+          <t>BUF:343901</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>1249</v>
+        <v>1225</v>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr"/>
@@ -8737,20 +8735,20 @@
       </c>
       <c r="CD36" t="inlineStr">
         <is>
-          <t>3qJ9B5zvT7$hh913fcAFEj</t>
+          <t>3qJ9B5zvT7$hh913fcAFEa</t>
         </is>
       </c>
       <c r="CE36" t="n">
         <v>1</v>
       </c>
       <c r="CF36" t="n">
-        <v>118.876854433513</v>
+        <v>36.0606998520392</v>
       </c>
       <c r="CG36" t="n">
-        <v>162.444519</v>
+        <v>25.4851555</v>
       </c>
       <c r="CH36" t="n">
-        <v>162.444519</v>
+        <v>25.4851555</v>
       </c>
       <c r="CI36" t="inlineStr">
         <is>
@@ -8780,7 +8778,7 @@
         <v>0</v>
       </c>
       <c r="CT36" t="n">
-        <v>162.444519</v>
+        <v>25.4851555</v>
       </c>
       <c r="CU36" t="n">
         <v>0</v>
@@ -8794,14 +8792,14 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>1250</v>
+        <v>1226</v>
       </c>
       <c r="B37" t="n">
-        <v>1209</v>
+        <v>1185</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>3AGSwy4Cv9YOBE5MpdNLQt</t>
+          <t>1DAsWzcd53mxYOR7lJYiHX</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -8821,11 +8819,11 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>BUF:343901</t>
+          <t>BUF:343907</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>1250</v>
+        <v>1226</v>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr"/>
@@ -8964,20 +8962,20 @@
       </c>
       <c r="CD37" t="inlineStr">
         <is>
-          <t>3qJ9B5zvT7$hh913fcAFEa</t>
+          <t>3qJ9B5zvT7$hh913fcAFEQ</t>
         </is>
       </c>
       <c r="CE37" t="n">
         <v>1</v>
       </c>
       <c r="CF37" t="n">
-        <v>36.0606998520392</v>
+        <v>12.0248764381316</v>
       </c>
       <c r="CG37" t="n">
-        <v>25.4851555</v>
+        <v>4.922164</v>
       </c>
       <c r="CH37" t="n">
-        <v>25.4851555</v>
+        <v>4.922164</v>
       </c>
       <c r="CI37" t="inlineStr">
         <is>
@@ -9007,7 +9005,7 @@
         <v>0</v>
       </c>
       <c r="CT37" t="n">
-        <v>25.4851555</v>
+        <v>4.922164</v>
       </c>
       <c r="CU37" t="n">
         <v>0</v>
@@ -9021,14 +9019,14 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>1251</v>
+        <v>1227</v>
       </c>
       <c r="B38" t="n">
-        <v>1209</v>
+        <v>1188</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>0E4QXUam15QfaVaTAymHn2</t>
+          <t>2jDi0spfj5xugCuK32MU8B</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -9048,11 +9046,11 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>BUF:343907</t>
+          <t>PAA:345416</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>1251</v>
+        <v>1227</v>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr"/>
@@ -9080,11 +9078,11 @@
       <c r="AB38" t="inlineStr"/>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>EG</t>
+          <t>OG3</t>
         </is>
       </c>
       <c r="AD38" t="n">
-        <v>0</v>
+        <v>11.948</v>
       </c>
       <c r="AE38" t="inlineStr"/>
       <c r="AF38" t="inlineStr"/>
@@ -9140,7 +9138,7 @@
       <c r="BR38" t="inlineStr"/>
       <c r="BS38" t="inlineStr">
         <is>
-          <t>BUF</t>
+          <t>PAA</t>
         </is>
       </c>
       <c r="BT38" t="inlineStr">
@@ -9155,17 +9153,17 @@
       </c>
       <c r="BV38" t="inlineStr">
         <is>
-          <t>Bearbeitet Umgebungsflächen</t>
+          <t>Pausenfläche PS</t>
         </is>
       </c>
       <c r="BW38" t="inlineStr">
         <is>
-          <t>Alle restlichen bearbeiteten Aussenanlagenflächen bis zur Grundstücksgrenze</t>
+          <t>Pausenfläche (Hartplatz) für ges.Schulanlage. Auf Erweiterungsbau sollen auch Dachflächen als Pausenplatz nutzbar sein</t>
         </is>
       </c>
       <c r="BX38" t="inlineStr">
         <is>
-          <t>BUF  -  Bearbeitet Umgebungsflächen</t>
+          <t>PAA  -  Pausenfläche PS</t>
         </is>
       </c>
       <c r="BY38" t="inlineStr">
@@ -9191,20 +9189,20 @@
       </c>
       <c r="CD38" t="inlineStr">
         <is>
-          <t>3qJ9B5zvT7$hh913fcAFEQ</t>
+          <t>2VFBkNPLX5hxPkFzLFhskt</t>
         </is>
       </c>
       <c r="CE38" t="n">
         <v>1</v>
       </c>
       <c r="CF38" t="n">
-        <v>12.0248764381316</v>
+        <v>61.8686530336046</v>
       </c>
       <c r="CG38" t="n">
-        <v>4.922164</v>
+        <v>125.579465</v>
       </c>
       <c r="CH38" t="n">
-        <v>4.922164</v>
+        <v>125.579465</v>
       </c>
       <c r="CI38" t="inlineStr">
         <is>
@@ -9213,18 +9211,22 @@
       </c>
       <c r="CJ38" t="inlineStr">
         <is>
-          <t>???</t>
-        </is>
-      </c>
-      <c r="CK38" t="inlineStr"/>
-      <c r="CL38" t="inlineStr"/>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="CK38" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="CL38" t="n">
+        <v>400</v>
+      </c>
       <c r="CM38" t="inlineStr"/>
       <c r="CN38" t="inlineStr"/>
       <c r="CO38" t="inlineStr"/>
       <c r="CP38" t="inlineStr"/>
       <c r="CQ38" t="inlineStr">
         <is>
-          <t>Aussenbereich_BUF</t>
+          <t>Aussenbereich_PAA</t>
         </is>
       </c>
       <c r="CR38" t="n">
@@ -9234,7 +9236,7 @@
         <v>0</v>
       </c>
       <c r="CT38" t="n">
-        <v>4.922164</v>
+        <v>0</v>
       </c>
       <c r="CU38" t="n">
         <v>0</v>
@@ -9243,19 +9245,19 @@
         <v>0</v>
       </c>
       <c r="CW38" t="n">
-        <v>0</v>
+        <v>125.579465</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>1252</v>
+        <v>1228</v>
       </c>
       <c r="B39" t="n">
-        <v>1212</v>
+        <v>1188</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>2MZESDDfb379fB261rIbnR</t>
+          <t>1JP2teRZzAKhVlWoAk44Gi</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -9279,7 +9281,7 @@
         </is>
       </c>
       <c r="H39" t="n">
-        <v>1252</v>
+        <v>1228</v>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr"/>
@@ -9311,7 +9313,7 @@
         </is>
       </c>
       <c r="AD39" t="n">
-        <v>11.947</v>
+        <v>11.948</v>
       </c>
       <c r="AE39" t="inlineStr"/>
       <c r="AF39" t="inlineStr"/>
@@ -9422,16 +9424,16 @@
         </is>
       </c>
       <c r="CE39" t="n">
-        <v>1.001</v>
+        <v>1</v>
       </c>
       <c r="CF39" t="n">
-        <v>61.8367587494543</v>
+        <v>61.8746072005705</v>
       </c>
       <c r="CG39" t="n">
-        <v>126.1984585</v>
+        <v>125.616293</v>
       </c>
       <c r="CH39" t="n">
-        <v>126.3246569585</v>
+        <v>125.616293</v>
       </c>
       <c r="CI39" t="inlineStr">
         <is>
@@ -9474,19 +9476,19 @@
         <v>0</v>
       </c>
       <c r="CW39" t="n">
-        <v>126.1984585</v>
+        <v>125.616293</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>1253</v>
+        <v>1229</v>
       </c>
       <c r="B40" t="n">
-        <v>1212</v>
+        <v>1185</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>2VPSmwn8f80wlwsZLQwj7f</t>
+          <t>2pH4Wqvuf1bu8FEuNmVz7e</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -9506,11 +9508,11 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>PAA:345416</t>
+          <t>ALL:343925</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>1253</v>
+        <v>1229</v>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr"/>
@@ -9538,11 +9540,11 @@
       <c r="AB40" t="inlineStr"/>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>OG3</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="AD40" t="n">
-        <v>11.947</v>
+        <v>0</v>
       </c>
       <c r="AE40" t="inlineStr"/>
       <c r="AF40" t="inlineStr"/>
@@ -9598,7 +9600,7 @@
       <c r="BR40" t="inlineStr"/>
       <c r="BS40" t="inlineStr">
         <is>
-          <t>PAA</t>
+          <t>ALL</t>
         </is>
       </c>
       <c r="BT40" t="inlineStr">
@@ -9613,17 +9615,17 @@
       </c>
       <c r="BV40" t="inlineStr">
         <is>
-          <t>Pausenfläche PS</t>
+          <t>Allwetterplatz mit Sportbelag</t>
         </is>
       </c>
       <c r="BW40" t="inlineStr">
         <is>
-          <t>Pausenfläche (Hartplatz) für ges.Schulanlage. Auf Erweiterungsbau sollen auch Dachflächen als Pausenplatz nutzbar sein</t>
+          <t>idealerweise 26 x 40m - ebenerdiger sportfunktionaler Allwetterplatz (EPDM-Belag, Ballfang) mit minimalen Spielfeld-Abmessungen 24 x 13m plus Sicherheitsraum umlaufend b=1m zwingend nachzuweisen</t>
         </is>
       </c>
       <c r="BX40" t="inlineStr">
         <is>
-          <t>PAA  -  Pausenfläche PS</t>
+          <t>ALL  -  Allwetterplatz mit Sportbelag</t>
         </is>
       </c>
       <c r="BY40" t="inlineStr">
@@ -9649,20 +9651,20 @@
       </c>
       <c r="CD40" t="inlineStr">
         <is>
-          <t>2VFBkNPLX5hxPkFzLFhskt</t>
+          <t>3qJ9B5zvT7$hh913fcAFEC</t>
         </is>
       </c>
       <c r="CE40" t="n">
-        <v>1.001</v>
+        <v>1</v>
       </c>
       <c r="CF40" t="n">
-        <v>61.8374883969868</v>
+        <v>82.51586312796729</v>
       </c>
       <c r="CG40" t="n">
-        <v>126.246645</v>
+        <v>396.6236325</v>
       </c>
       <c r="CH40" t="n">
-        <v>126.372891645</v>
+        <v>396.6236325</v>
       </c>
       <c r="CI40" t="inlineStr">
         <is>
@@ -9675,10 +9677,10 @@
         </is>
       </c>
       <c r="CK40" t="n">
-        <v>10.8</v>
+        <v>10.4</v>
       </c>
       <c r="CL40" t="n">
-        <v>400</v>
+        <v>390</v>
       </c>
       <c r="CM40" t="inlineStr"/>
       <c r="CN40" t="inlineStr"/>
@@ -9686,7 +9688,7 @@
       <c r="CP40" t="inlineStr"/>
       <c r="CQ40" t="inlineStr">
         <is>
-          <t>Aussenbereich_PAA</t>
+          <t>Aussenbereich_ALL</t>
         </is>
       </c>
       <c r="CR40" t="n">
@@ -9696,7 +9698,7 @@
         <v>0</v>
       </c>
       <c r="CT40" t="n">
-        <v>0</v>
+        <v>396.6236325</v>
       </c>
       <c r="CU40" t="n">
         <v>0</v>
@@ -9705,19 +9707,19 @@
         <v>0</v>
       </c>
       <c r="CW40" t="n">
-        <v>126.246645</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>1254</v>
+        <v>1230</v>
       </c>
       <c r="B41" t="n">
-        <v>1209</v>
+        <v>1185</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>2VcirkfBf6ahuppLqfjuCo</t>
+          <t>1y6$NkJCn2eRH9vQ05Vfth</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -9737,11 +9739,11 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>ALL:343925</t>
+          <t>PPA:343898</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>1254</v>
+        <v>1230</v>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr"/>
@@ -9829,7 +9831,7 @@
       <c r="BR41" t="inlineStr"/>
       <c r="BS41" t="inlineStr">
         <is>
-          <t>ALL</t>
+          <t>PPA</t>
         </is>
       </c>
       <c r="BT41" t="inlineStr">
@@ -9844,17 +9846,17 @@
       </c>
       <c r="BV41" t="inlineStr">
         <is>
-          <t>Allwetterplatz mit Sportbelag</t>
+          <t>Parkplätze PW (Normbedarf)</t>
         </is>
       </c>
       <c r="BW41" t="inlineStr">
         <is>
-          <t>idealerweise 26 x 40m - ebenerdiger sportfunktionaler Allwetterplatz (EPDM-Belag, Ballfang) mit minimalen Spielfeld-Abmessungen 24 x 13m plus Sicherheitsraum umlaufend b=1m zwingend nachzuweisen</t>
+          <t>Gesamtangebot für Schulpersonal, Besuchende, Anlieferung, IV-Transport usw. Reduktionsfaktor nicht berücksichtigt&amp;#10;1 PP-IV auf Anlage, 5 PP ausgelagert in TG vom GFA Wildbach, Wildbachstr. 11</t>
         </is>
       </c>
       <c r="BX41" t="inlineStr">
         <is>
-          <t>ALL  -  Allwetterplatz mit Sportbelag</t>
+          <t>PPA  -  Parkplätze PW (Normbedarf)</t>
         </is>
       </c>
       <c r="BY41" t="inlineStr">
@@ -9880,20 +9882,20 @@
       </c>
       <c r="CD41" t="inlineStr">
         <is>
-          <t>3qJ9B5zvT7$hh913fcAFEC</t>
+          <t>3qJ9B5zvT7$hh913fcAFEZ</t>
         </is>
       </c>
       <c r="CE41" t="n">
         <v>1</v>
       </c>
       <c r="CF41" t="n">
-        <v>82.51586312796729</v>
+        <v>20.3229188998477</v>
       </c>
       <c r="CG41" t="n">
-        <v>396.6236325</v>
+        <v>17.289957</v>
       </c>
       <c r="CH41" t="n">
-        <v>396.6236325</v>
+        <v>17.289957</v>
       </c>
       <c r="CI41" t="inlineStr">
         <is>
@@ -9906,10 +9908,10 @@
         </is>
       </c>
       <c r="CK41" t="n">
-        <v>10.4</v>
+        <v>10.1</v>
       </c>
       <c r="CL41" t="n">
-        <v>390</v>
+        <v>12</v>
       </c>
       <c r="CM41" t="inlineStr"/>
       <c r="CN41" t="inlineStr"/>
@@ -9917,7 +9919,7 @@
       <c r="CP41" t="inlineStr"/>
       <c r="CQ41" t="inlineStr">
         <is>
-          <t>Aussenbereich_ALL</t>
+          <t>Aussenbereich_PPA</t>
         </is>
       </c>
       <c r="CR41" t="n">
@@ -9927,7 +9929,7 @@
         <v>0</v>
       </c>
       <c r="CT41" t="n">
-        <v>396.6236325</v>
+        <v>17.289957</v>
       </c>
       <c r="CU41" t="n">
         <v>0</v>
@@ -9941,14 +9943,14 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>1255</v>
+        <v>1231</v>
       </c>
       <c r="B42" t="n">
-        <v>1209</v>
+        <v>1185</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>07p_i19HfFMxUYszLXHx0R</t>
+          <t>0a48Ih65rFx8QfDnXMMhEl</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -9968,11 +9970,11 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>PPA:343898</t>
+          <t>VEL_L:343934</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>1255</v>
+        <v>1231</v>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr"/>
@@ -10060,7 +10062,7 @@
       <c r="BR42" t="inlineStr"/>
       <c r="BS42" t="inlineStr">
         <is>
-          <t>PPA</t>
+          <t>VEL_L</t>
         </is>
       </c>
       <c r="BT42" t="inlineStr">
@@ -10075,17 +10077,17 @@
       </c>
       <c r="BV42" t="inlineStr">
         <is>
-          <t>Parkplätze PW (Normbedarf)</t>
+          <t>Velo- Abstellplätze Schulpersonal</t>
         </is>
       </c>
       <c r="BW42" t="inlineStr">
         <is>
-          <t>Gesamtangebot für Schulpersonal, Besuchende, Anlieferung, IV-Transport usw. Reduktionsfaktor nicht berücksichtigt&amp;#10;1 PP-IV auf Anlage, 5 PP ausgelagert in TG vom GFA Wildbach, Wildbachstr. 11</t>
+          <t>8 Stück, Gedeckt und gegen Diebstahl und Vanalismus geschützt</t>
         </is>
       </c>
       <c r="BX42" t="inlineStr">
         <is>
-          <t>PPA  -  Parkplätze PW (Normbedarf)</t>
+          <t>VEL_L  -  Velo- Abstellplätze Schulpersonal</t>
         </is>
       </c>
       <c r="BY42" t="inlineStr">
@@ -10111,20 +10113,20 @@
       </c>
       <c r="CD42" t="inlineStr">
         <is>
-          <t>3qJ9B5zvT7$hh913fcAFEZ</t>
+          <t>3qJ9B5zvT7$hh913fcAFE7</t>
         </is>
       </c>
       <c r="CE42" t="n">
         <v>1</v>
       </c>
       <c r="CF42" t="n">
-        <v>20.3229188998477</v>
+        <v>9.201563573455161</v>
       </c>
       <c r="CG42" t="n">
-        <v>17.289957</v>
+        <v>5.20168</v>
       </c>
       <c r="CH42" t="n">
-        <v>17.289957</v>
+        <v>5.20168</v>
       </c>
       <c r="CI42" t="inlineStr">
         <is>
@@ -10133,22 +10135,20 @@
       </c>
       <c r="CJ42" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>false</t>
         </is>
       </c>
       <c r="CK42" t="n">
         <v>10.1</v>
       </c>
-      <c r="CL42" t="n">
-        <v>12</v>
-      </c>
+      <c r="CL42" t="inlineStr"/>
       <c r="CM42" t="inlineStr"/>
       <c r="CN42" t="inlineStr"/>
       <c r="CO42" t="inlineStr"/>
       <c r="CP42" t="inlineStr"/>
       <c r="CQ42" t="inlineStr">
         <is>
-          <t>Aussenbereich_PPA</t>
+          <t>Aussenbereich_VEL_L</t>
         </is>
       </c>
       <c r="CR42" t="n">
@@ -10158,7 +10158,7 @@
         <v>0</v>
       </c>
       <c r="CT42" t="n">
-        <v>17.289957</v>
+        <v>5.20168</v>
       </c>
       <c r="CU42" t="n">
         <v>0</v>
@@ -10172,14 +10172,14 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>1256</v>
+        <v>1232</v>
       </c>
       <c r="B43" t="n">
-        <v>1209</v>
+        <v>1185</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>3dUr5q39zEXBCsj4PLV405</t>
+          <t>3sBsqaQPb0euZE5Csd1V40</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -10203,7 +10203,7 @@
         </is>
       </c>
       <c r="H43" t="n">
-        <v>1256</v>
+        <v>1232</v>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr"/>
@@ -10346,16 +10346,16 @@
         </is>
       </c>
       <c r="CE43" t="n">
-        <v>1</v>
+        <v>1.00000564844451</v>
       </c>
       <c r="CF43" t="n">
-        <v>36.5379660958738</v>
+        <v>36.5380755997099</v>
       </c>
       <c r="CG43" t="n">
-        <v>73.566976</v>
+        <v>73.5662785</v>
       </c>
       <c r="CH43" t="n">
-        <v>73.566976</v>
+        <v>73.5666940350422</v>
       </c>
       <c r="CI43" t="inlineStr">
         <is>
@@ -10387,7 +10387,7 @@
         <v>0</v>
       </c>
       <c r="CT43" t="n">
-        <v>73.566976</v>
+        <v>73.5662785</v>
       </c>
       <c r="CU43" t="n">
         <v>0</v>
@@ -10401,14 +10401,14 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>1257</v>
+        <v>1233</v>
       </c>
       <c r="B44" t="n">
-        <v>1209</v>
+        <v>1185</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>3WAjbS9Tz63fT8SRxhsEgW</t>
+          <t>2jZ_u9g6bC0gnFdRULl6Ao</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -10432,7 +10432,7 @@
         </is>
       </c>
       <c r="H44" t="n">
-        <v>1257</v>
+        <v>1233</v>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr"/>
@@ -10632,14 +10632,14 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>1258</v>
+        <v>1234</v>
       </c>
       <c r="B45" t="n">
-        <v>1209</v>
+        <v>1185</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>2F9RWBhUfEZ8$cJ_kTeVpx</t>
+          <t>0owNcgsrLCORAeZymoLxMZ</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -10663,7 +10663,7 @@
         </is>
       </c>
       <c r="H45" t="n">
-        <v>1258</v>
+        <v>1234</v>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr"/>
@@ -10802,16 +10802,16 @@
         </is>
       </c>
       <c r="CE45" t="n">
-        <v>1</v>
+        <v>1.00001430884626</v>
       </c>
       <c r="CF45" t="n">
-        <v>70.7275988525333</v>
+        <v>70.7243967332807</v>
       </c>
       <c r="CG45" t="n">
-        <v>295.86007</v>
+        <v>295.8120275</v>
       </c>
       <c r="CH45" t="n">
-        <v>295.86007</v>
+        <v>295.816260228824</v>
       </c>
       <c r="CI45" t="inlineStr">
         <is>
@@ -10845,7 +10845,7 @@
         <v>0</v>
       </c>
       <c r="CT45" t="n">
-        <v>295.86007</v>
+        <v>295.8120275</v>
       </c>
       <c r="CU45" t="n">
         <v>0</v>
@@ -10859,14 +10859,14 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>1259</v>
+        <v>1235</v>
       </c>
       <c r="B46" t="n">
-        <v>1209</v>
+        <v>1185</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>3vBeHUwhfB5OcVQruWBfzN</t>
+          <t>0cuCI57f5FDx6c5xjTH_wt</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -10890,7 +10890,7 @@
         </is>
       </c>
       <c r="H46" t="n">
-        <v>1259</v>
+        <v>1235</v>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr"/>
@@ -11036,13 +11036,13 @@
         <v>1</v>
       </c>
       <c r="CF46" t="n">
-        <v>228.018781084836</v>
+        <v>228.018850694891</v>
       </c>
       <c r="CG46" t="n">
-        <v>627.669683</v>
+        <v>627.6705645</v>
       </c>
       <c r="CH46" t="n">
-        <v>627.669683</v>
+        <v>627.6705645</v>
       </c>
       <c r="CI46" t="inlineStr">
         <is>
@@ -11076,7 +11076,7 @@
         <v>0</v>
       </c>
       <c r="CT46" t="n">
-        <v>627.669683</v>
+        <v>627.6705645</v>
       </c>
       <c r="CU46" t="n">
         <v>0</v>
@@ -11090,14 +11090,14 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>1260</v>
+        <v>1236</v>
       </c>
       <c r="B47" t="n">
-        <v>1207</v>
+        <v>1183</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>3LuW9jHbHBBAyJit_$Yn3$</t>
+          <t>3EFA13Ox1F58pYx6_i5NyU</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -11121,7 +11121,7 @@
         </is>
       </c>
       <c r="H47" t="n">
-        <v>1260</v>
+        <v>1236</v>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="J47" t="inlineStr"/>
@@ -11264,7 +11264,7 @@
         </is>
       </c>
       <c r="CE47" t="n">
-        <v>4.121</v>
+        <v>4.12</v>
       </c>
       <c r="CF47" t="n">
         <v>57.8747961939876</v>
@@ -11273,7 +11273,7 @@
         <v>130.4597315</v>
       </c>
       <c r="CH47" t="n">
-        <v>537.6245535115</v>
+        <v>537.49409378</v>
       </c>
       <c r="CI47" t="inlineStr">
         <is>
@@ -11319,14 +11319,14 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>1261</v>
+        <v>1237</v>
       </c>
       <c r="B48" t="n">
-        <v>1207</v>
+        <v>1183</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>0ZrdVUR4b0zxBrw6VrPmpy</t>
+          <t>0VzQ2RIZnBkuyXmMpvbN9_</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -11350,7 +11350,7 @@
         </is>
       </c>
       <c r="H48" t="n">
-        <v>1261</v>
+        <v>1237</v>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="J48" t="inlineStr"/>
@@ -11493,7 +11493,7 @@
         </is>
       </c>
       <c r="CE48" t="n">
-        <v>4.121</v>
+        <v>4.12</v>
       </c>
       <c r="CF48" t="n">
         <v>29.2296306506672</v>
@@ -11502,7 +11502,7 @@
         <v>38.861445</v>
       </c>
       <c r="CH48" t="n">
-        <v>160.148014845</v>
+        <v>160.1091534</v>
       </c>
       <c r="CI48" t="inlineStr">
         <is>
@@ -11548,14 +11548,14 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>1262</v>
+        <v>1238</v>
       </c>
       <c r="B49" t="n">
-        <v>1208</v>
+        <v>1184</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>1R9Imo_5167B$XHbYy7aZ6</t>
+          <t>0bebBo2BjBix6YQ7lpTjg5</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -11579,7 +11579,7 @@
         </is>
       </c>
       <c r="H49" t="n">
-        <v>1262</v>
+        <v>1238</v>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="J49" t="inlineStr"/>
@@ -11722,7 +11722,7 @@
         </is>
       </c>
       <c r="CE49" t="n">
-        <v>3.421</v>
+        <v>3.42</v>
       </c>
       <c r="CF49" t="n">
         <v>21.5722949304711</v>
@@ -11731,7 +11731,7 @@
         <v>25.280915</v>
       </c>
       <c r="CH49" t="n">
-        <v>86.48601021499999</v>
+        <v>86.4607293</v>
       </c>
       <c r="CI49" t="inlineStr">
         <is>
@@ -11777,14 +11777,14 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>1263</v>
+        <v>1239</v>
       </c>
       <c r="B50" t="n">
-        <v>1209</v>
+        <v>1185</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>0teRCO0lj5OQYpPkvQztRq</t>
+          <t>0p4XPibzXDmfYuHdDNQKoi</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -11808,7 +11808,7 @@
         </is>
       </c>
       <c r="H50" t="n">
-        <v>1263</v>
+        <v>1239</v>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="J50" t="inlineStr"/>
@@ -11950,13 +11950,13 @@
         <v>1</v>
       </c>
       <c r="CF50" t="n">
-        <v>32.1201520903664</v>
+        <v>32.1152224910364</v>
       </c>
       <c r="CG50" t="n">
-        <v>34.123994</v>
+        <v>34.1596555</v>
       </c>
       <c r="CH50" t="n">
-        <v>34.123994</v>
+        <v>34.1596555</v>
       </c>
       <c r="CI50" t="inlineStr">
         <is>
@@ -11986,7 +11986,7 @@
         <v>0</v>
       </c>
       <c r="CT50" t="n">
-        <v>34.123994</v>
+        <v>34.1596555</v>
       </c>
       <c r="CU50" t="n">
         <v>0</v>
@@ -12000,14 +12000,14 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>1264</v>
+        <v>1240</v>
       </c>
       <c r="B51" t="n">
-        <v>1209</v>
+        <v>1185</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>3O5OUxbKP5_PZAUUrtfSgZ</t>
+          <t>3vzyyhvhTCCxHI3Ujz_Pdk</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -12031,7 +12031,7 @@
         </is>
       </c>
       <c r="H51" t="n">
-        <v>1264</v>
+        <v>1240</v>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="J51" t="inlineStr"/>
@@ -12177,13 +12177,13 @@
         <v>3</v>
       </c>
       <c r="CF51" t="n">
-        <v>13.0853052853127</v>
+        <v>13.1107742818786</v>
       </c>
       <c r="CG51" t="n">
-        <v>13.396027</v>
+        <v>13.502395</v>
       </c>
       <c r="CH51" t="n">
-        <v>40.188081</v>
+        <v>40.507185</v>
       </c>
       <c r="CI51" t="inlineStr">
         <is>
@@ -12213,7 +12213,7 @@
         <v>0</v>
       </c>
       <c r="CT51" t="n">
-        <v>13.396027</v>
+        <v>13.502395</v>
       </c>
       <c r="CU51" t="n">
         <v>0</v>
@@ -12227,14 +12227,14 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>1265</v>
+        <v>1241</v>
       </c>
       <c r="B52" t="n">
-        <v>1207</v>
+        <v>1183</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>2v3d7GGqDEd8IyrTdRXWWY</t>
+          <t>3P24pHOeX7huTaoUa46vgT</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -12258,7 +12258,7 @@
         </is>
       </c>
       <c r="H52" t="n">
-        <v>1265</v>
+        <v>1241</v>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="J52" t="inlineStr"/>
@@ -12401,7 +12401,7 @@
         </is>
       </c>
       <c r="CE52" t="n">
-        <v>4.121</v>
+        <v>4.11999999999999</v>
       </c>
       <c r="CF52" t="n">
         <v>33.6781770938313</v>
@@ -12410,7 +12410,7 @@
         <v>68.07347249999999</v>
       </c>
       <c r="CH52" t="n">
-        <v>280.5307801725</v>
+        <v>280.462706699999</v>
       </c>
       <c r="CI52" t="inlineStr">
         <is>
@@ -12456,14 +12456,14 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>1266</v>
+        <v>1242</v>
       </c>
       <c r="B53" t="n">
-        <v>1208</v>
+        <v>1184</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>2_kl8xFAvE_Oi0Djmy1jeA</t>
+          <t>0OAGNaNgv3wwzf3ckQ_KTm</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -12487,7 +12487,7 @@
         </is>
       </c>
       <c r="H53" t="n">
-        <v>1266</v>
+        <v>1242</v>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="J53" t="inlineStr"/>
@@ -12630,7 +12630,7 @@
         </is>
       </c>
       <c r="CE53" t="n">
-        <v>3.421</v>
+        <v>3.42</v>
       </c>
       <c r="CF53" t="n">
         <v>15.2440637556325</v>
@@ -12639,7 +12639,7 @@
         <v>13.790366</v>
       </c>
       <c r="CH53" t="n">
-        <v>47.176842086</v>
+        <v>47.16305172</v>
       </c>
       <c r="CI53" t="inlineStr">
         <is>
@@ -12685,14 +12685,14 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>1267</v>
+        <v>1243</v>
       </c>
       <c r="B54" t="n">
-        <v>1208</v>
+        <v>1184</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>1wnl70Hcf4J91aH6kWoQ5w</t>
+          <t>2pxOd96v91mxlwof2bdwwu</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -12716,7 +12716,7 @@
         </is>
       </c>
       <c r="H54" t="n">
-        <v>1267</v>
+        <v>1243</v>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="J54" t="inlineStr"/>
@@ -12859,7 +12859,7 @@
         </is>
       </c>
       <c r="CE54" t="n">
-        <v>3.421</v>
+        <v>3.42</v>
       </c>
       <c r="CF54" t="n">
         <v>7.93463321095369</v>
@@ -12868,7 +12868,7 @@
         <v>3.934619</v>
       </c>
       <c r="CH54" t="n">
-        <v>13.460331599</v>
+        <v>13.45639698</v>
       </c>
       <c r="CI54" t="inlineStr">
         <is>
@@ -12912,14 +12912,14 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>1268</v>
+        <v>1244</v>
       </c>
       <c r="B55" t="n">
-        <v>1210</v>
+        <v>1186</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>1MPw1r9hv6$h6AZYdCPJK4</t>
+          <t>2lK1NiaZXE9g_b2KyM_qzf</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -12943,7 +12943,7 @@
         </is>
       </c>
       <c r="H55" t="n">
-        <v>1268</v>
+        <v>1244</v>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="J55" t="inlineStr"/>
@@ -13139,14 +13139,14 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>1269</v>
+        <v>1245</v>
       </c>
       <c r="B56" t="n">
-        <v>1208</v>
+        <v>1184</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>1F3Fkq$vj7GQErmS_ow7lc</t>
+          <t>2DRzef4hn3IgIiLgkhkHE9</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -13170,7 +13170,7 @@
         </is>
       </c>
       <c r="H56" t="n">
-        <v>1269</v>
+        <v>1245</v>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="J56" t="inlineStr"/>
@@ -13313,7 +13313,7 @@
         </is>
       </c>
       <c r="CE56" t="n">
-        <v>3.421</v>
+        <v>3.42</v>
       </c>
       <c r="CF56" t="n">
         <v>16.0088117114571</v>
@@ -13322,7 +13322,7 @@
         <v>15.551871</v>
       </c>
       <c r="CH56" t="n">
-        <v>53.202950691</v>
+        <v>53.18739882</v>
       </c>
       <c r="CI56" t="inlineStr">
         <is>
@@ -13366,14 +13366,14 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>1270</v>
+        <v>1246</v>
       </c>
       <c r="B57" t="n">
-        <v>1208</v>
+        <v>1184</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>1acftYr2jDufGYUUZLoAmB</t>
+          <t>2EaietiEbAIPhvSO2Cvy$b</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -13397,7 +13397,7 @@
         </is>
       </c>
       <c r="H57" t="n">
-        <v>1270</v>
+        <v>1246</v>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="J57" t="inlineStr"/>
@@ -13540,7 +13540,7 @@
         </is>
       </c>
       <c r="CE57" t="n">
-        <v>3.421</v>
+        <v>3.42</v>
       </c>
       <c r="CF57" t="n">
         <v>16.1179353577298</v>
@@ -13549,7 +13549,7 @@
         <v>15.807475</v>
       </c>
       <c r="CH57" t="n">
-        <v>54.077371975</v>
+        <v>54.0615645</v>
       </c>
       <c r="CI57" t="inlineStr">
         <is>
@@ -13593,14 +13593,14 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>1271</v>
+        <v>1247</v>
       </c>
       <c r="B58" t="n">
-        <v>1208</v>
+        <v>1184</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>1vDbowLhr7nx5SdmnF8FXc</t>
+          <t>2_ozTiGP19wxfIiizV$YDP</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -13624,7 +13624,7 @@
         </is>
       </c>
       <c r="H58" t="n">
-        <v>1271</v>
+        <v>1247</v>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="J58" t="inlineStr"/>
@@ -13767,16 +13767,16 @@
         </is>
       </c>
       <c r="CE58" t="n">
-        <v>3.421</v>
+        <v>3.42</v>
       </c>
       <c r="CF58" t="n">
-        <v>38.5924363426088</v>
+        <v>38.4721477169385</v>
       </c>
       <c r="CG58" t="n">
-        <v>42.344828</v>
+        <v>42.594047</v>
       </c>
       <c r="CH58" t="n">
-        <v>144.861656588</v>
+        <v>145.67164074</v>
       </c>
       <c r="CI58" t="inlineStr">
         <is>
@@ -13803,7 +13803,7 @@
         <v>0</v>
       </c>
       <c r="CS58" t="n">
-        <v>42.344828</v>
+        <v>42.594047</v>
       </c>
       <c r="CT58" t="n">
         <v>0</v>
@@ -13820,14 +13820,14 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>1272</v>
+        <v>1248</v>
       </c>
       <c r="B59" t="n">
-        <v>1208</v>
+        <v>1184</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>2oV52czXD7zAOL8XOUSL78</t>
+          <t>1hrw6SBSX5_xz0kjcf$lQq</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -13851,7 +13851,7 @@
         </is>
       </c>
       <c r="H59" t="n">
-        <v>1272</v>
+        <v>1248</v>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="J59" t="inlineStr"/>
@@ -13994,16 +13994,16 @@
         </is>
       </c>
       <c r="CE59" t="n">
-        <v>3.421</v>
+        <v>3.4200048337541</v>
       </c>
       <c r="CF59" t="n">
-        <v>38.5665051072028</v>
+        <v>38.4494075508202</v>
       </c>
       <c r="CG59" t="n">
-        <v>42.0894875</v>
+        <v>42.33211</v>
       </c>
       <c r="CH59" t="n">
-        <v>143.9881367375</v>
+        <v>144.77602082301</v>
       </c>
       <c r="CI59" t="inlineStr">
         <is>
@@ -14030,7 +14030,7 @@
         <v>0</v>
       </c>
       <c r="CS59" t="n">
-        <v>42.0894875</v>
+        <v>42.33211</v>
       </c>
       <c r="CT59" t="n">
         <v>0</v>
@@ -14047,14 +14047,14 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>1273</v>
+        <v>1249</v>
       </c>
       <c r="B60" t="n">
-        <v>1210</v>
+        <v>1185</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>1FDFHpwUH4NB1tapjSpmKb</t>
+          <t>1KAZImcajE19VMZ2urkS9A</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -14074,11 +14074,11 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>SGR:342955</t>
+          <t>AGS:343922</t>
         </is>
       </c>
       <c r="H60" t="n">
-        <v>1273</v>
+        <v>1249</v>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="J60" t="inlineStr"/>
@@ -14093,7 +14093,7 @@
       <c r="S60" t="inlineStr"/>
       <c r="T60" t="inlineStr">
         <is>
-          <t>INTERNAL</t>
+          <t>EXTERNAL</t>
         </is>
       </c>
       <c r="U60" t="inlineStr"/>
@@ -14106,11 +14106,11 @@
       <c r="AB60" t="inlineStr"/>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>OG1</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="AD60" t="n">
-        <v>2.998</v>
+        <v>0</v>
       </c>
       <c r="AE60" t="inlineStr"/>
       <c r="AF60" t="inlineStr"/>
@@ -14166,7 +14166,7 @@
       <c r="BR60" t="inlineStr"/>
       <c r="BS60" t="inlineStr">
         <is>
-          <t>SGR</t>
+          <t>AGS</t>
         </is>
       </c>
       <c r="BT60" t="inlineStr">
@@ -14181,17 +14181,17 @@
       </c>
       <c r="BV60" t="inlineStr">
         <is>
-          <t>Geräteraum</t>
+          <t>Aussengeräteraum Sport</t>
         </is>
       </c>
       <c r="BW60" t="inlineStr">
         <is>
-          <t>Diekt aus der zugehörigen Sporthalle, stufenlos zugänglich. Inkl. abschliessbarem Kleingeräteraum. Zu beachten: Mind. 6m Raumtiefe und 2.5m Höhe im Licht.</t>
+          <t>Direkter Zugang von Aussen,mit Beleuchtung und Ballkompressor</t>
         </is>
       </c>
       <c r="BX60" t="inlineStr">
         <is>
-          <t>SGR  -  Geräteraum</t>
+          <t>AGS  -  Aussengeräteraum Sport</t>
         </is>
       </c>
       <c r="BY60" t="inlineStr">
@@ -14203,7 +14203,7 @@
         <v>1</v>
       </c>
       <c r="CA60" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="CB60" t="inlineStr">
         <is>
@@ -14217,20 +14217,20 @@
       </c>
       <c r="CD60" t="inlineStr">
         <is>
-          <t>0b93QOWH141xpbKCpGErNi</t>
+          <t>3qJ9B5zvT7$hh913fcAFEB</t>
         </is>
       </c>
       <c r="CE60" t="n">
-        <v>3.982</v>
+        <v>1</v>
       </c>
       <c r="CF60" t="n">
-        <v>41.7997852969898</v>
+        <v>15.9988743322313</v>
       </c>
       <c r="CG60" t="n">
-        <v>89.581008</v>
+        <v>14.9977755</v>
       </c>
       <c r="CH60" t="n">
-        <v>356.711573856</v>
+        <v>14.9977755</v>
       </c>
       <c r="CI60" t="inlineStr">
         <is>
@@ -14242,7 +14242,7 @@
         <v>4.1</v>
       </c>
       <c r="CL60" t="n">
-        <v>90</v>
+        <v>15</v>
       </c>
       <c r="CM60" t="inlineStr"/>
       <c r="CN60" t="inlineStr"/>
@@ -14250,7 +14250,7 @@
       <c r="CP60" t="inlineStr"/>
       <c r="CQ60" t="inlineStr">
         <is>
-          <t>Sportbereich_SGR</t>
+          <t>Sportbereich_AGS</t>
         </is>
       </c>
       <c r="CR60" t="n">
@@ -14260,10 +14260,10 @@
         <v>0</v>
       </c>
       <c r="CT60" t="n">
-        <v>0</v>
+        <v>14.9977755</v>
       </c>
       <c r="CU60" t="n">
-        <v>89.581008</v>
+        <v>0</v>
       </c>
       <c r="CV60" t="n">
         <v>0</v>
@@ -14274,14 +14274,14 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>1274</v>
+        <v>1250</v>
       </c>
       <c r="B61" t="n">
-        <v>1209</v>
+        <v>1184</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>0qoMVDV8fAzBp8ww__y4Tz</t>
+          <t>3MbScePwXCG951Z0r4L0yN</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -14301,11 +14301,11 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>AGS:343922</t>
+          <t>GSA:342369</t>
         </is>
       </c>
       <c r="H61" t="n">
-        <v>1274</v>
+        <v>1250</v>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="J61" t="inlineStr"/>
@@ -14320,7 +14320,7 @@
       <c r="S61" t="inlineStr"/>
       <c r="T61" t="inlineStr">
         <is>
-          <t>EXTERNAL</t>
+          <t>INTERNAL</t>
         </is>
       </c>
       <c r="U61" t="inlineStr"/>
@@ -14333,11 +14333,11 @@
       <c r="AB61" t="inlineStr"/>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>EG</t>
+          <t>UG1</t>
         </is>
       </c>
       <c r="AD61" t="n">
-        <v>0</v>
+        <v>-3.78</v>
       </c>
       <c r="AE61" t="inlineStr"/>
       <c r="AF61" t="inlineStr"/>
@@ -14393,7 +14393,7 @@
       <c r="BR61" t="inlineStr"/>
       <c r="BS61" t="inlineStr">
         <is>
-          <t>AGS</t>
+          <t>GSA</t>
         </is>
       </c>
       <c r="BT61" t="inlineStr">
@@ -14408,17 +14408,17 @@
       </c>
       <c r="BV61" t="inlineStr">
         <is>
-          <t>Aussengeräteraum Sport</t>
+          <t>Garderobe inkl. Dusche</t>
         </is>
       </c>
       <c r="BW61" t="inlineStr">
         <is>
-          <t>Direkter Zugang von Aussen,mit Beleuchtung und Ballkompressor</t>
+          <t>Garderoben gem. BASPO 201. Jede Umkleide schliesst direkt an einen Duschraum an. &amp;#10;Inkl. Abtrockungszone, Garderoben gem. BASPO 201. Pro Duschraum ist 1 gehbehindertengerechter Duschplatz vorhanden.</t>
         </is>
       </c>
       <c r="BX61" t="inlineStr">
         <is>
-          <t>AGS  -  Aussengeräteraum Sport</t>
+          <t>GSA  -  Garderobe inkl. Dusche</t>
         </is>
       </c>
       <c r="BY61" t="inlineStr">
@@ -14430,7 +14430,7 @@
         <v>1</v>
       </c>
       <c r="CA61" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="CB61" t="inlineStr">
         <is>
@@ -14444,32 +14444,32 @@
       </c>
       <c r="CD61" t="inlineStr">
         <is>
-          <t>3qJ9B5zvT7$hh913fcAFEB</t>
+          <t>1QH5Axl111J9SJj2E3W4wD</t>
         </is>
       </c>
       <c r="CE61" t="n">
-        <v>1</v>
+        <v>3.4200029159233</v>
       </c>
       <c r="CF61" t="n">
-        <v>15.9988743322313</v>
+        <v>38.4766189708997</v>
       </c>
       <c r="CG61" t="n">
-        <v>14.9977755</v>
+        <v>42.543861</v>
       </c>
       <c r="CH61" t="n">
-        <v>14.9977755</v>
+        <v>145.500128674635</v>
       </c>
       <c r="CI61" t="inlineStr">
         <is>
-          <t>HNF</t>
+          <t>NNF</t>
         </is>
       </c>
       <c r="CJ61" t="inlineStr"/>
       <c r="CK61" t="n">
-        <v>4.1</v>
+        <v>7.2</v>
       </c>
       <c r="CL61" t="n">
-        <v>15</v>
+        <v>45</v>
       </c>
       <c r="CM61" t="inlineStr"/>
       <c r="CN61" t="inlineStr"/>
@@ -14477,17 +14477,17 @@
       <c r="CP61" t="inlineStr"/>
       <c r="CQ61" t="inlineStr">
         <is>
-          <t>Sportbereich_AGS</t>
+          <t>Sportbereich_GSA</t>
         </is>
       </c>
       <c r="CR61" t="n">
         <v>0</v>
       </c>
       <c r="CS61" t="n">
-        <v>0</v>
+        <v>42.543861</v>
       </c>
       <c r="CT61" t="n">
-        <v>14.9977755</v>
+        <v>0</v>
       </c>
       <c r="CU61" t="n">
         <v>0</v>
@@ -14501,14 +14501,14 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>1275</v>
+        <v>1251</v>
       </c>
       <c r="B62" t="n">
-        <v>1208</v>
+        <v>1184</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>1d_UGp1UD2pfCq6QCu1odj</t>
+          <t>3YWB1QD45A0ffgE_grSlSK</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -14528,11 +14528,11 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>GSA:342369</t>
+          <t>GSA:342372</t>
         </is>
       </c>
       <c r="H62" t="n">
-        <v>1275</v>
+        <v>1251</v>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="J62" t="inlineStr"/>
@@ -14671,20 +14671,20 @@
       </c>
       <c r="CD62" t="inlineStr">
         <is>
-          <t>1QH5Axl111J9SJj2E3W4wD</t>
+          <t>1QH5Axl111J9SJj2E3W4w8</t>
         </is>
       </c>
       <c r="CE62" t="n">
-        <v>3.421</v>
+        <v>3.42</v>
       </c>
       <c r="CF62" t="n">
-        <v>38.597841235775</v>
+        <v>38.3845491226873</v>
       </c>
       <c r="CG62" t="n">
-        <v>42.293608</v>
+        <v>42.138849</v>
       </c>
       <c r="CH62" t="n">
-        <v>144.686432968</v>
+        <v>144.11486358</v>
       </c>
       <c r="CI62" t="inlineStr">
         <is>
@@ -14711,7 +14711,7 @@
         <v>0</v>
       </c>
       <c r="CS62" t="n">
-        <v>42.293608</v>
+        <v>42.138849</v>
       </c>
       <c r="CT62" t="n">
         <v>0</v>
@@ -14728,14 +14728,14 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>1276</v>
+        <v>1252</v>
       </c>
       <c r="B63" t="n">
-        <v>1208</v>
+        <v>1183</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>1DjBk084n8gfRcElXcnhlR</t>
+          <t>0fphzOn3z3ffzYnIZDfkRZ</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -14755,11 +14755,11 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>GSA:342372</t>
+          <t>SGR:340482</t>
         </is>
       </c>
       <c r="H63" t="n">
-        <v>1276</v>
+        <v>1252</v>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="J63" t="inlineStr"/>
@@ -14787,11 +14787,11 @@
       <c r="AB63" t="inlineStr"/>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>UG1</t>
+          <t>UG2</t>
         </is>
       </c>
       <c r="AD63" t="n">
-        <v>-3.78</v>
+        <v>-8.199999999999999</v>
       </c>
       <c r="AE63" t="inlineStr"/>
       <c r="AF63" t="inlineStr"/>
@@ -14847,7 +14847,7 @@
       <c r="BR63" t="inlineStr"/>
       <c r="BS63" t="inlineStr">
         <is>
-          <t>GSA</t>
+          <t>SGR</t>
         </is>
       </c>
       <c r="BT63" t="inlineStr">
@@ -14862,17 +14862,17 @@
       </c>
       <c r="BV63" t="inlineStr">
         <is>
-          <t>Garderobe inkl. Dusche</t>
+          <t>Geräteraum</t>
         </is>
       </c>
       <c r="BW63" t="inlineStr">
         <is>
-          <t>Garderoben gem. BASPO 201. Jede Umkleide schliesst direkt an einen Duschraum an. &amp;#10;Inkl. Abtrockungszone, Garderoben gem. BASPO 201. Pro Duschraum ist 1 gehbehindertengerechter Duschplatz vorhanden.</t>
+          <t>Diekt aus der zugehörigen Sporthalle, stufenlos zugänglich. Inkl. abschliessbarem Kleingeräteraum. Zu beachten: Mind. 6m Raumtiefe und 2.5m Höhe im Licht.</t>
         </is>
       </c>
       <c r="BX63" t="inlineStr">
         <is>
-          <t>GSA  -  Garderobe inkl. Dusche</t>
+          <t>SGR  -  Geräteraum</t>
         </is>
       </c>
       <c r="BY63" t="inlineStr">
@@ -14884,7 +14884,7 @@
         <v>1</v>
       </c>
       <c r="CA63" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="CB63" t="inlineStr">
         <is>
@@ -14898,32 +14898,32 @@
       </c>
       <c r="CD63" t="inlineStr">
         <is>
-          <t>1QH5Axl111J9SJj2E3W4w8</t>
+          <t>3VbCMl1_928hbAKPG5Knzn</t>
         </is>
       </c>
       <c r="CE63" t="n">
-        <v>3.421</v>
+        <v>4.12</v>
       </c>
       <c r="CF63" t="n">
-        <v>38.5011315279237</v>
+        <v>37.9925325891083</v>
       </c>
       <c r="CG63" t="n">
-        <v>41.894542</v>
+        <v>89.857005</v>
       </c>
       <c r="CH63" t="n">
-        <v>143.321228182</v>
+        <v>370.2108606</v>
       </c>
       <c r="CI63" t="inlineStr">
         <is>
-          <t>NNF</t>
+          <t>HNF</t>
         </is>
       </c>
       <c r="CJ63" t="inlineStr"/>
       <c r="CK63" t="n">
-        <v>7.2</v>
+        <v>4.1</v>
       </c>
       <c r="CL63" t="n">
-        <v>45</v>
+        <v>90</v>
       </c>
       <c r="CM63" t="inlineStr"/>
       <c r="CN63" t="inlineStr"/>
@@ -14931,14 +14931,14 @@
       <c r="CP63" t="inlineStr"/>
       <c r="CQ63" t="inlineStr">
         <is>
-          <t>Sportbereich_GSA</t>
+          <t>Sportbereich_SGR</t>
         </is>
       </c>
       <c r="CR63" t="n">
-        <v>0</v>
+        <v>89.857005</v>
       </c>
       <c r="CS63" t="n">
-        <v>41.894542</v>
+        <v>0</v>
       </c>
       <c r="CT63" t="n">
         <v>0</v>
@@ -14955,14 +14955,14 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>1277</v>
+        <v>1253</v>
       </c>
       <c r="B64" t="n">
-        <v>1210</v>
+        <v>1186</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>2qwEpCHpPBQhWqR0aH8a_c</t>
+          <t>3$MWY95kL37xnSaojxj3cW</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -14982,11 +14982,11 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>SPH:342964</t>
+          <t>SGR:342955</t>
         </is>
       </c>
       <c r="H64" t="n">
-        <v>1277</v>
+        <v>1253</v>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="J64" t="inlineStr"/>
@@ -15074,7 +15074,7 @@
       <c r="BR64" t="inlineStr"/>
       <c r="BS64" t="inlineStr">
         <is>
-          <t>SPH</t>
+          <t>SGR</t>
         </is>
       </c>
       <c r="BT64" t="inlineStr">
@@ -15089,17 +15089,17 @@
       </c>
       <c r="BV64" t="inlineStr">
         <is>
-          <t>Sporthalle</t>
+          <t>Geräteraum</t>
         </is>
       </c>
       <c r="BW64" t="inlineStr">
         <is>
-          <t>Einfachhalle 28 x 16 x 7m (frei bespielbare Höhe= 7m, Stauraum für Technik, Tragstruktur, Sportgeräte + ca. 1m)&amp;#10;</t>
+          <t>Diekt aus der zugehörigen Sporthalle, stufenlos zugänglich. Inkl. abschliessbarem Kleingeräteraum. Zu beachten: Mind. 6m Raumtiefe und 2.5m Höhe im Licht.</t>
         </is>
       </c>
       <c r="BX64" t="inlineStr">
         <is>
-          <t>SPH  -  Sporthalle</t>
+          <t>SGR  -  Geräteraum</t>
         </is>
       </c>
       <c r="BY64" t="inlineStr">
@@ -15125,20 +15125,20 @@
       </c>
       <c r="CD64" t="inlineStr">
         <is>
-          <t>0b93QOWH141xpbKCpGErNp</t>
+          <t>0b93QOWH141xpbKCpGErNi</t>
         </is>
       </c>
       <c r="CE64" t="n">
-        <v>7.85999999999999</v>
+        <v>3.982</v>
       </c>
       <c r="CF64" t="n">
-        <v>89.09855519173711</v>
+        <v>41.7997852969898</v>
       </c>
       <c r="CG64" t="n">
-        <v>463.384951</v>
+        <v>89.581008</v>
       </c>
       <c r="CH64" t="n">
-        <v>3642.20571486</v>
+        <v>356.711573856</v>
       </c>
       <c r="CI64" t="inlineStr">
         <is>
@@ -15147,26 +15147,18 @@
       </c>
       <c r="CJ64" t="inlineStr"/>
       <c r="CK64" t="n">
-        <v>5.5</v>
+        <v>4.1</v>
       </c>
       <c r="CL64" t="n">
-        <v>448</v>
-      </c>
-      <c r="CM64" t="n">
-        <v>7</v>
-      </c>
-      <c r="CN64" t="n">
-        <v>8</v>
-      </c>
-      <c r="CO64" t="n">
-        <v>28</v>
-      </c>
-      <c r="CP64" t="n">
-        <v>16</v>
-      </c>
+        <v>90</v>
+      </c>
+      <c r="CM64" t="inlineStr"/>
+      <c r="CN64" t="inlineStr"/>
+      <c r="CO64" t="inlineStr"/>
+      <c r="CP64" t="inlineStr"/>
       <c r="CQ64" t="inlineStr">
         <is>
-          <t>Sportbereich_SPH</t>
+          <t>Sportbereich_SGR</t>
         </is>
       </c>
       <c r="CR64" t="n">
@@ -15179,7 +15171,7 @@
         <v>0</v>
       </c>
       <c r="CU64" t="n">
-        <v>463.384951</v>
+        <v>89.581008</v>
       </c>
       <c r="CV64" t="n">
         <v>0</v>
@@ -15190,14 +15182,14 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>1278</v>
+        <v>1254</v>
       </c>
       <c r="B65" t="n">
-        <v>1207</v>
+        <v>1183</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>1OOeb7pNP5YhVqjcacSVQj</t>
+          <t>0SfLsfaY1DQQexHNkqpPq8</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -15217,11 +15209,11 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>SGR:340482</t>
+          <t>HRR:340470</t>
         </is>
       </c>
       <c r="H65" t="n">
-        <v>1278</v>
+        <v>1254</v>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="J65" t="inlineStr"/>
@@ -15309,32 +15301,32 @@
       <c r="BR65" t="inlineStr"/>
       <c r="BS65" t="inlineStr">
         <is>
-          <t>SGR</t>
+          <t>HRR</t>
         </is>
       </c>
       <c r="BT65" t="inlineStr">
         <is>
-          <t>Sportbereich</t>
+          <t>Hausdienst</t>
         </is>
       </c>
       <c r="BU65" t="inlineStr">
         <is>
-          <t>Sporthallen</t>
+          <t>Hausdienst</t>
         </is>
       </c>
       <c r="BV65" t="inlineStr">
         <is>
-          <t>Geräteraum</t>
+          <t>Hauptreinigungsraum</t>
         </is>
       </c>
       <c r="BW65" t="inlineStr">
         <is>
-          <t>Diekt aus der zugehörigen Sporthalle, stufenlos zugänglich. Inkl. abschliessbarem Kleingeräteraum. Zu beachten: Mind. 6m Raumtiefe und 2.5m Höhe im Licht.</t>
+          <t>1 pro Gebäude/Trakt, im UG, Lager, Kaltwasseranschluss und Ausgusslavabo, Bodenablauf (Im Geschoss des HRR kein RRG)&amp;#10;</t>
         </is>
       </c>
       <c r="BX65" t="inlineStr">
         <is>
-          <t>SGR  -  Geräteraum</t>
+          <t>HRR  -  Hauptreinigungsraum</t>
         </is>
       </c>
       <c r="BY65" t="inlineStr">
@@ -15346,7 +15338,7 @@
         <v>1</v>
       </c>
       <c r="CA65" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="CB65" t="inlineStr">
         <is>
@@ -15360,32 +15352,32 @@
       </c>
       <c r="CD65" t="inlineStr">
         <is>
-          <t>3VbCMl1_928hbAKPG5Knzn</t>
+          <t>3VbCMl1_928hbAKPG5Kno5</t>
         </is>
       </c>
       <c r="CE65" t="n">
-        <v>4.121</v>
+        <v>4.12000209952917</v>
       </c>
       <c r="CF65" t="n">
-        <v>37.9925325891083</v>
+        <v>25.4721434358016</v>
       </c>
       <c r="CG65" t="n">
-        <v>89.857005</v>
+        <v>24.251362</v>
       </c>
       <c r="CH65" t="n">
-        <v>370.300717605</v>
+        <v>99.9156623564419</v>
       </c>
       <c r="CI65" t="inlineStr">
         <is>
-          <t>HNF</t>
+          <t>NNF</t>
         </is>
       </c>
       <c r="CJ65" t="inlineStr"/>
       <c r="CK65" t="n">
-        <v>4.1</v>
+        <v>7.1</v>
       </c>
       <c r="CL65" t="n">
-        <v>90</v>
+        <v>25</v>
       </c>
       <c r="CM65" t="inlineStr"/>
       <c r="CN65" t="inlineStr"/>
@@ -15393,11 +15385,11 @@
       <c r="CP65" t="inlineStr"/>
       <c r="CQ65" t="inlineStr">
         <is>
-          <t>Sportbereich_SGR</t>
+          <t>Hausdienst_HRR</t>
         </is>
       </c>
       <c r="CR65" t="n">
-        <v>89.857005</v>
+        <v>24.251362</v>
       </c>
       <c r="CS65" t="n">
         <v>0</v>
@@ -15417,14 +15409,14 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>1279</v>
+        <v>1255</v>
       </c>
       <c r="B66" t="n">
-        <v>1207</v>
+        <v>1183</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>0kB0A2S5z5auQg3$i3qAjO</t>
+          <t>2jQqxIN7D0G9XrN3psKCHB</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -15444,11 +15436,11 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>HRR:340470</t>
+          <t>GRP:340476</t>
         </is>
       </c>
       <c r="H66" t="n">
-        <v>1279</v>
+        <v>1255</v>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="J66" t="inlineStr"/>
@@ -15536,7 +15528,7 @@
       <c r="BR66" t="inlineStr"/>
       <c r="BS66" t="inlineStr">
         <is>
-          <t>HRR</t>
+          <t>GRP</t>
         </is>
       </c>
       <c r="BT66" t="inlineStr">
@@ -15551,17 +15543,17 @@
       </c>
       <c r="BV66" t="inlineStr">
         <is>
-          <t>Hauptreinigungsraum</t>
+          <t>Garderobe / Personalraum</t>
         </is>
       </c>
       <c r="BW66" t="inlineStr">
         <is>
-          <t>1 pro Gebäude/Trakt, im UG, Lager, Kaltwasseranschluss und Ausgusslavabo, Bodenablauf (Im Geschoss des HRR kein RRG)&amp;#10;</t>
+          <t>Spinden + Umkleidekabinen</t>
         </is>
       </c>
       <c r="BX66" t="inlineStr">
         <is>
-          <t>HRR  -  Hauptreinigungsraum</t>
+          <t>GRP  -  Garderobe / Personalraum</t>
         </is>
       </c>
       <c r="BY66" t="inlineStr">
@@ -15587,20 +15579,20 @@
       </c>
       <c r="CD66" t="inlineStr">
         <is>
-          <t>3VbCMl1_928hbAKPG5Kno5</t>
+          <t>3VbCMl1_928hbAKPG5KnoF</t>
         </is>
       </c>
       <c r="CE66" t="n">
-        <v>4.121</v>
+        <v>4.12</v>
       </c>
       <c r="CF66" t="n">
-        <v>25.4703597146799</v>
+        <v>13.5853049126557</v>
       </c>
       <c r="CG66" t="n">
-        <v>24.194584</v>
+        <v>11.5049595</v>
       </c>
       <c r="CH66" t="n">
-        <v>99.70588066400001</v>
+        <v>47.40043314</v>
       </c>
       <c r="CI66" t="inlineStr">
         <is>
@@ -15609,10 +15601,10 @@
       </c>
       <c r="CJ66" t="inlineStr"/>
       <c r="CK66" t="n">
-        <v>7.1</v>
+        <v>7.2</v>
       </c>
       <c r="CL66" t="n">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="CM66" t="inlineStr"/>
       <c r="CN66" t="inlineStr"/>
@@ -15620,11 +15612,11 @@
       <c r="CP66" t="inlineStr"/>
       <c r="CQ66" t="inlineStr">
         <is>
-          <t>Hausdienst_HRR</t>
+          <t>Hausdienst_GRP</t>
         </is>
       </c>
       <c r="CR66" t="n">
-        <v>24.194584</v>
+        <v>11.5049595</v>
       </c>
       <c r="CS66" t="n">
         <v>0</v>
@@ -15644,14 +15636,14 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>1280</v>
+        <v>1256</v>
       </c>
       <c r="B67" t="n">
-        <v>1207</v>
+        <v>1185</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>21ftMaN2H3x9V_1Iuv7_Lz</t>
+          <t>1elxkk8h12l8VI66SES48s</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -15671,11 +15663,11 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>GRP:340476</t>
+          <t>CON:342808</t>
         </is>
       </c>
       <c r="H67" t="n">
-        <v>1280</v>
+        <v>1256</v>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="J67" t="inlineStr"/>
@@ -15703,11 +15695,11 @@
       <c r="AB67" t="inlineStr"/>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>UG2</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="AD67" t="n">
-        <v>-8.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="AE67" t="inlineStr"/>
       <c r="AF67" t="inlineStr"/>
@@ -15763,7 +15755,7 @@
       <c r="BR67" t="inlineStr"/>
       <c r="BS67" t="inlineStr">
         <is>
-          <t>GRP</t>
+          <t>CON</t>
         </is>
       </c>
       <c r="BT67" t="inlineStr">
@@ -15778,17 +15770,17 @@
       </c>
       <c r="BV67" t="inlineStr">
         <is>
-          <t>Garderobe / Personalraum</t>
+          <t xml:space="preserve">Containerraum </t>
         </is>
       </c>
       <c r="BW67" t="inlineStr">
         <is>
-          <t>Spinden + Umkleidekabinen</t>
+          <t>Container: 0.8 x 1.25 m, 800L Inhalt, Zugang direkt von Aussen</t>
         </is>
       </c>
       <c r="BX67" t="inlineStr">
         <is>
-          <t>GRP  -  Garderobe / Personalraum</t>
+          <t xml:space="preserve">CON  -  Containerraum </t>
         </is>
       </c>
       <c r="BY67" t="inlineStr">
@@ -15814,20 +15806,20 @@
       </c>
       <c r="CD67" t="inlineStr">
         <is>
-          <t>3VbCMl1_928hbAKPG5KnoF</t>
+          <t>3$FY_ljDfBsweJfZwnfjOv</t>
         </is>
       </c>
       <c r="CE67" t="n">
-        <v>4.121</v>
+        <v>3</v>
       </c>
       <c r="CF67" t="n">
-        <v>13.5853049126557</v>
+        <v>13.3093771618808</v>
       </c>
       <c r="CG67" t="n">
-        <v>11.5049595</v>
+        <v>11.070615</v>
       </c>
       <c r="CH67" t="n">
-        <v>47.4119380995</v>
+        <v>33.211845</v>
       </c>
       <c r="CI67" t="inlineStr">
         <is>
@@ -15836,7 +15828,7 @@
       </c>
       <c r="CJ67" t="inlineStr"/>
       <c r="CK67" t="n">
-        <v>7.2</v>
+        <v>7.3</v>
       </c>
       <c r="CL67" t="n">
         <v>12</v>
@@ -15847,17 +15839,17 @@
       <c r="CP67" t="inlineStr"/>
       <c r="CQ67" t="inlineStr">
         <is>
-          <t>Hausdienst_GRP</t>
+          <t>Hausdienst_CON</t>
         </is>
       </c>
       <c r="CR67" t="n">
-        <v>11.5049595</v>
+        <v>0</v>
       </c>
       <c r="CS67" t="n">
         <v>0</v>
       </c>
       <c r="CT67" t="n">
-        <v>0</v>
+        <v>11.070615</v>
       </c>
       <c r="CU67" t="n">
         <v>0</v>
@@ -15871,14 +15863,14 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>1281</v>
+        <v>1257</v>
       </c>
       <c r="B68" t="n">
-        <v>1209</v>
+        <v>1183</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>2rnYpcA2j5ORd2uupGEvG0</t>
+          <t>1mK10My2H1Jf6TH2FFyNJl</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -15898,11 +15890,11 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>CON:342808</t>
+          <t>SPH:340222</t>
         </is>
       </c>
       <c r="H68" t="n">
-        <v>1281</v>
+        <v>1257</v>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="J68" t="inlineStr"/>
@@ -15930,11 +15922,11 @@
       <c r="AB68" t="inlineStr"/>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>EG</t>
+          <t>UG2</t>
         </is>
       </c>
       <c r="AD68" t="n">
-        <v>0</v>
+        <v>-8.199999999999999</v>
       </c>
       <c r="AE68" t="inlineStr"/>
       <c r="AF68" t="inlineStr"/>
@@ -15990,32 +15982,32 @@
       <c r="BR68" t="inlineStr"/>
       <c r="BS68" t="inlineStr">
         <is>
-          <t>CON</t>
+          <t>SPH</t>
         </is>
       </c>
       <c r="BT68" t="inlineStr">
         <is>
-          <t>Hausdienst</t>
+          <t>Sportbereich</t>
         </is>
       </c>
       <c r="BU68" t="inlineStr">
         <is>
-          <t>Hausdienst</t>
+          <t>Sporthallen</t>
         </is>
       </c>
       <c r="BV68" t="inlineStr">
         <is>
-          <t xml:space="preserve">Containerraum </t>
+          <t>Sporthalle</t>
         </is>
       </c>
       <c r="BW68" t="inlineStr">
         <is>
-          <t>Container: 0.8 x 1.25 m, 800L Inhalt, Zugang direkt von Aussen</t>
+          <t>Einfachhalle 28 x 16 x 7m (frei bespielbare Höhe= 7m, Stauraum für Technik, Tragstruktur, Sportgeräte + ca. 1m)&amp;#10;</t>
         </is>
       </c>
       <c r="BX68" t="inlineStr">
         <is>
-          <t xml:space="preserve">CON  -  Containerraum </t>
+          <t>SPH  -  Sporthalle</t>
         </is>
       </c>
       <c r="BY68" t="inlineStr">
@@ -16027,7 +16019,7 @@
         <v>1</v>
       </c>
       <c r="CA68" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="CB68" t="inlineStr">
         <is>
@@ -16041,50 +16033,58 @@
       </c>
       <c r="CD68" t="inlineStr">
         <is>
-          <t>3$FY_ljDfBsweJfZwnfjOv</t>
+          <t>27eKs3mJf3tucFrDswOcPu</t>
         </is>
       </c>
       <c r="CE68" t="n">
-        <v>3</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="CF68" t="n">
-        <v>13.3093771618808</v>
+        <v>89.0980990398666</v>
       </c>
       <c r="CG68" t="n">
-        <v>11.070615</v>
+        <v>463.376039</v>
       </c>
       <c r="CH68" t="n">
-        <v>33.211845</v>
+        <v>3799.6835198</v>
       </c>
       <c r="CI68" t="inlineStr">
         <is>
-          <t>NNF</t>
+          <t>HNF</t>
         </is>
       </c>
       <c r="CJ68" t="inlineStr"/>
       <c r="CK68" t="n">
-        <v>7.3</v>
+        <v>5.5</v>
       </c>
       <c r="CL68" t="n">
-        <v>12</v>
-      </c>
-      <c r="CM68" t="inlineStr"/>
-      <c r="CN68" t="inlineStr"/>
-      <c r="CO68" t="inlineStr"/>
-      <c r="CP68" t="inlineStr"/>
+        <v>448</v>
+      </c>
+      <c r="CM68" t="n">
+        <v>7</v>
+      </c>
+      <c r="CN68" t="n">
+        <v>8</v>
+      </c>
+      <c r="CO68" t="n">
+        <v>28</v>
+      </c>
+      <c r="CP68" t="n">
+        <v>16</v>
+      </c>
       <c r="CQ68" t="inlineStr">
         <is>
-          <t>Hausdienst_CON</t>
+          <t>Sportbereich_SPH</t>
         </is>
       </c>
       <c r="CR68" t="n">
-        <v>0</v>
+        <v>463.376039</v>
       </c>
       <c r="CS68" t="n">
         <v>0</v>
       </c>
       <c r="CT68" t="n">
-        <v>11.070615</v>
+        <v>0</v>
       </c>
       <c r="CU68" t="n">
         <v>0</v>
@@ -16098,14 +16098,14 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>1282</v>
+        <v>1258</v>
       </c>
       <c r="B69" t="n">
-        <v>1207</v>
+        <v>1186</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>3fqw08GKT8VB$WT6lvspWB</t>
+          <t>0v8vKsFUHEhuGCI94TqyuL</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -16125,11 +16125,11 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>SPH:340222</t>
+          <t>SPH:342964</t>
         </is>
       </c>
       <c r="H69" t="n">
-        <v>1282</v>
+        <v>1258</v>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="J69" t="inlineStr"/>
@@ -16157,11 +16157,11 @@
       <c r="AB69" t="inlineStr"/>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>UG2</t>
+          <t>OG1</t>
         </is>
       </c>
       <c r="AD69" t="n">
-        <v>-8.199999999999999</v>
+        <v>2.998</v>
       </c>
       <c r="AE69" t="inlineStr"/>
       <c r="AF69" t="inlineStr"/>
@@ -16268,20 +16268,20 @@
       </c>
       <c r="CD69" t="inlineStr">
         <is>
-          <t>27eKs3mJf3tucFrDswOcPu</t>
+          <t>0b93QOWH141xpbKCpGErNp</t>
         </is>
       </c>
       <c r="CE69" t="n">
-        <v>8.199999999999999</v>
+        <v>7.85999999999999</v>
       </c>
       <c r="CF69" t="n">
-        <v>89.0980990398666</v>
+        <v>89.09855519173711</v>
       </c>
       <c r="CG69" t="n">
-        <v>463.376039</v>
+        <v>463.384951</v>
       </c>
       <c r="CH69" t="n">
-        <v>3799.6835198</v>
+        <v>3642.20571486</v>
       </c>
       <c r="CI69" t="inlineStr">
         <is>
@@ -16313,7 +16313,7 @@
         </is>
       </c>
       <c r="CR69" t="n">
-        <v>463.376039</v>
+        <v>0</v>
       </c>
       <c r="CS69" t="n">
         <v>0</v>
@@ -16322,7 +16322,7 @@
         <v>0</v>
       </c>
       <c r="CU69" t="n">
-        <v>0</v>
+        <v>463.384951</v>
       </c>
       <c r="CV69" t="n">
         <v>0</v>
@@ -16333,14 +16333,14 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>1283</v>
+        <v>1259</v>
       </c>
       <c r="B70" t="n">
-        <v>1208</v>
+        <v>1184</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>3fS1w73ELCBRUIqHWvP3$z</t>
+          <t>25qvKAslv4su4AGnfPnQAy</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -16364,7 +16364,7 @@
         </is>
       </c>
       <c r="H70" t="n">
-        <v>1283</v>
+        <v>1259</v>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="J70" t="inlineStr"/>
@@ -16507,16 +16507,16 @@
         </is>
       </c>
       <c r="CE70" t="n">
-        <v>3.421</v>
+        <v>3.42000189301365</v>
       </c>
       <c r="CF70" t="n">
-        <v>9.480715967371051</v>
+        <v>9.600782029985609</v>
       </c>
       <c r="CG70" t="n">
-        <v>3.582502</v>
+        <v>3.639574</v>
       </c>
       <c r="CH70" t="n">
-        <v>12.255739342</v>
+        <v>12.4473499697633</v>
       </c>
       <c r="CI70" t="inlineStr">
         <is>
@@ -16543,7 +16543,7 @@
         <v>0</v>
       </c>
       <c r="CS70" t="n">
-        <v>3.582502</v>
+        <v>3.639574</v>
       </c>
       <c r="CT70" t="n">
         <v>0</v>
@@ -16560,14 +16560,14 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>1284</v>
+        <v>1260</v>
       </c>
       <c r="B71" t="n">
-        <v>1211</v>
+        <v>1187</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>2FQ8B6_JP08wqgDmUUSwZn</t>
+          <t>0$R0qHln98kepMxkmwzDXO</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -16591,7 +16591,7 @@
         </is>
       </c>
       <c r="H71" t="n">
-        <v>1284</v>
+        <v>1260</v>
       </c>
       <c r="I71" t="inlineStr"/>
       <c r="J71" t="inlineStr"/>
@@ -16623,7 +16623,7 @@
         </is>
       </c>
       <c r="AD71" t="n">
-        <v>7.939</v>
+        <v>7.94</v>
       </c>
       <c r="AE71" t="inlineStr"/>
       <c r="AF71" t="inlineStr"/>
@@ -16734,7 +16734,7 @@
         </is>
       </c>
       <c r="CE71" t="n">
-        <v>3.579</v>
+        <v>3.578</v>
       </c>
       <c r="CF71" t="n">
         <v>8.46504079502658</v>
@@ -16743,7 +16743,7 @@
         <v>4.3787245</v>
       </c>
       <c r="CH71" t="n">
-        <v>15.6714549855</v>
+        <v>15.667076261</v>
       </c>
       <c r="CI71" t="inlineStr">
         <is>
@@ -16787,14 +16787,14 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>1285</v>
+        <v>1261</v>
       </c>
       <c r="B72" t="n">
-        <v>1209</v>
+        <v>1185</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>1PXOCrKLD2ohK81bqcw5L8</t>
+          <t>1nHVq1BLj3N83VoxI$QAiV</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -16818,7 +16818,7 @@
         </is>
       </c>
       <c r="H72" t="n">
-        <v>1285</v>
+        <v>1261</v>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="J72" t="inlineStr"/>
@@ -17010,14 +17010,14 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>1286</v>
+        <v>1262</v>
       </c>
       <c r="B73" t="n">
-        <v>1212</v>
+        <v>1188</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>3gQV9bpHv7NfVbjzlui7Lj</t>
+          <t>3865N6dr5D2QZmKnsV5UjA</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -17041,7 +17041,7 @@
         </is>
       </c>
       <c r="H73" t="n">
-        <v>1286</v>
+        <v>1262</v>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="J73" t="inlineStr"/>
@@ -17073,7 +17073,7 @@
         </is>
       </c>
       <c r="AD73" t="n">
-        <v>11.947</v>
+        <v>11.948</v>
       </c>
       <c r="AE73" t="inlineStr"/>
       <c r="AF73" t="inlineStr"/>
@@ -17233,14 +17233,14 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>1287</v>
+        <v>1263</v>
       </c>
       <c r="B74" t="n">
-        <v>1212</v>
+        <v>1188</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>0x5OAt7GXB6Rq0gRG_tICL</t>
+          <t>2dCF9Z2NrCiPs79T_2XETx</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -17264,7 +17264,7 @@
         </is>
       </c>
       <c r="H74" t="n">
-        <v>1287</v>
+        <v>1263</v>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="J74" t="inlineStr"/>
@@ -17296,7 +17296,7 @@
         </is>
       </c>
       <c r="AD74" t="n">
-        <v>11.947</v>
+        <v>11.948</v>
       </c>
       <c r="AE74" t="inlineStr"/>
       <c r="AF74" t="inlineStr"/>
@@ -17456,14 +17456,14 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>1288</v>
+        <v>1264</v>
       </c>
       <c r="B75" t="n">
-        <v>1211</v>
+        <v>1187</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>0CmilJIZr6B8RyG4QW7HcZ</t>
+          <t>2V_TDJQGX5u9IXI55MWQFM</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -17487,7 +17487,7 @@
         </is>
       </c>
       <c r="H75" t="n">
-        <v>1288</v>
+        <v>1264</v>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="J75" t="inlineStr"/>
@@ -17519,7 +17519,7 @@
         </is>
       </c>
       <c r="AD75" t="n">
-        <v>7.939</v>
+        <v>7.94</v>
       </c>
       <c r="AE75" t="inlineStr"/>
       <c r="AF75" t="inlineStr"/>
@@ -17626,7 +17626,7 @@
         </is>
       </c>
       <c r="CE75" t="n">
-        <v>3.579</v>
+        <v>3.578</v>
       </c>
       <c r="CF75" t="n">
         <v>29.9183857421605</v>
@@ -17635,7 +17635,7 @@
         <v>51.768942</v>
       </c>
       <c r="CH75" t="n">
-        <v>185.281043418</v>
+        <v>185.229274476</v>
       </c>
       <c r="CI75" t="inlineStr">
         <is>
@@ -17679,14 +17679,14 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>1289</v>
+        <v>1265</v>
       </c>
       <c r="B76" t="n">
-        <v>1211</v>
+        <v>1187</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>0mgHCA5Bj2q8PGPshAJwdu</t>
+          <t>2EdAa2vnvDwv$K313aI9nH</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -17710,7 +17710,7 @@
         </is>
       </c>
       <c r="H76" t="n">
-        <v>1289</v>
+        <v>1265</v>
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="J76" t="inlineStr"/>
@@ -17742,7 +17742,7 @@
         </is>
       </c>
       <c r="AD76" t="n">
-        <v>7.939</v>
+        <v>7.94</v>
       </c>
       <c r="AE76" t="inlineStr"/>
       <c r="AF76" t="inlineStr"/>
@@ -17849,7 +17849,7 @@
         </is>
       </c>
       <c r="CE76" t="n">
-        <v>3.579</v>
+        <v>3.578</v>
       </c>
       <c r="CF76" t="n">
         <v>16.922049437983</v>
@@ -17858,7 +17858,7 @@
         <v>17.5731125</v>
       </c>
       <c r="CH76" t="n">
-        <v>62.8941696375</v>
+        <v>62.876596525</v>
       </c>
       <c r="CI76" t="inlineStr">
         <is>
@@ -17902,14 +17902,14 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>1290</v>
+        <v>1266</v>
       </c>
       <c r="B77" t="n">
-        <v>1212</v>
+        <v>1188</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>3542EqJCz3j9Eu7i7LwKQI</t>
+          <t>2RQb_YuIX0cupTG8njrqa5</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -17933,7 +17933,7 @@
         </is>
       </c>
       <c r="H77" t="n">
-        <v>1290</v>
+        <v>1266</v>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="J77" t="inlineStr"/>
@@ -17965,7 +17965,7 @@
         </is>
       </c>
       <c r="AD77" t="n">
-        <v>11.947</v>
+        <v>11.948</v>
       </c>
       <c r="AE77" t="inlineStr"/>
       <c r="AF77" t="inlineStr"/>
@@ -18125,14 +18125,14 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>1291</v>
+        <v>1267</v>
       </c>
       <c r="B78" t="n">
-        <v>1209</v>
+        <v>1185</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>37pvr1fmPFoPR8VqDaFSaH</t>
+          <t>1xAkayK$92b8rEYvsI7ddA</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -18156,7 +18156,7 @@
         </is>
       </c>
       <c r="H78" t="n">
-        <v>1291</v>
+        <v>1267</v>
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="J78" t="inlineStr"/>
@@ -18354,14 +18354,14 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>1292</v>
+        <v>1268</v>
       </c>
       <c r="B79" t="n">
-        <v>1209</v>
+        <v>1185</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>2q$FhMpurDpQLxyHcG7QMH</t>
+          <t>0snplPWT179OZgXqJkFdam</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -18385,7 +18385,7 @@
         </is>
       </c>
       <c r="H79" t="n">
-        <v>1292</v>
+        <v>1268</v>
       </c>
       <c r="I79" t="inlineStr"/>
       <c r="J79" t="inlineStr"/>
@@ -18581,14 +18581,14 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>1293</v>
+        <v>1269</v>
       </c>
       <c r="B80" t="n">
-        <v>1209</v>
+        <v>1185</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>15q5B8t2H1jOLW$YLJTSCd</t>
+          <t>3QuKuIVNvEDebBjhENRHdp</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -18612,7 +18612,7 @@
         </is>
       </c>
       <c r="H80" t="n">
-        <v>1293</v>
+        <v>1269</v>
       </c>
       <c r="I80" t="inlineStr"/>
       <c r="J80" t="inlineStr"/>
@@ -18808,14 +18808,14 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>1294</v>
+        <v>1270</v>
       </c>
       <c r="B81" t="n">
-        <v>1209</v>
+        <v>1185</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>0lrhQ1hBL3UB9wu$bziAIW</t>
+          <t>1PFX2sV$1EtwB4cgbdYiiR</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -18839,7 +18839,7 @@
         </is>
       </c>
       <c r="H81" t="n">
-        <v>1294</v>
+        <v>1270</v>
       </c>
       <c r="I81" t="inlineStr"/>
       <c r="J81" t="inlineStr"/>
@@ -19031,14 +19031,14 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>1295</v>
+        <v>1271</v>
       </c>
       <c r="B82" t="n">
-        <v>1208</v>
+        <v>1184</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>1K1FlaQx1EExBCUKfCbQFS</t>
+          <t>2TkX3v9lLDHfNhAwV_173q</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -19062,7 +19062,7 @@
         </is>
       </c>
       <c r="H82" t="n">
-        <v>1295</v>
+        <v>1271</v>
       </c>
       <c r="I82" t="inlineStr"/>
       <c r="J82" t="inlineStr"/>
@@ -19205,7 +19205,7 @@
         </is>
       </c>
       <c r="CE82" t="n">
-        <v>3.421</v>
+        <v>3.42</v>
       </c>
       <c r="CF82" t="n">
         <v>7.37292153872654</v>
@@ -19214,7 +19214,7 @@
         <v>2.719245</v>
       </c>
       <c r="CH82" t="n">
-        <v>9.302537145000001</v>
+        <v>9.299817900000001</v>
       </c>
       <c r="CI82" t="inlineStr">
         <is>
@@ -19258,14 +19258,14 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>1296</v>
+        <v>1272</v>
       </c>
       <c r="B83" t="n">
-        <v>1208</v>
+        <v>1184</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>2VOStX3MjEzAywBgrc2Ymz</t>
+          <t>2b761ZbMf7OQyYTjBYwlqS</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -19289,7 +19289,7 @@
         </is>
       </c>
       <c r="H83" t="n">
-        <v>1296</v>
+        <v>1272</v>
       </c>
       <c r="I83" t="inlineStr"/>
       <c r="J83" t="inlineStr"/>
@@ -19432,7 +19432,7 @@
         </is>
       </c>
       <c r="CE83" t="n">
-        <v>3.421</v>
+        <v>3.42</v>
       </c>
       <c r="CF83" t="n">
         <v>7.50486180797826</v>
@@ -19441,7 +19441,7 @@
         <v>2.8944635</v>
       </c>
       <c r="CH83" t="n">
-        <v>9.901959633500001</v>
+        <v>9.89906517</v>
       </c>
       <c r="CI83" t="inlineStr">
         <is>
@@ -19485,14 +19485,14 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>1297</v>
+        <v>1273</v>
       </c>
       <c r="B84" t="n">
-        <v>1209</v>
+        <v>1185</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>1nbtU4bcH2MeFbv04K7ZN2</t>
+          <t>3th3YBjLPEbgeAFO8BnVLM</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -19516,7 +19516,7 @@
         </is>
       </c>
       <c r="H84" t="n">
-        <v>1297</v>
+        <v>1273</v>
       </c>
       <c r="I84" t="inlineStr"/>
       <c r="J84" t="inlineStr"/>
@@ -19714,14 +19714,14 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>1298</v>
+        <v>1274</v>
       </c>
       <c r="B85" t="n">
-        <v>1209</v>
+        <v>1185</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>1H1NJxt1P4dhBGOFdbv$N4</t>
+          <t>3V04x_Gn9CsOd3mf5kjSS7</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -19745,7 +19745,7 @@
         </is>
       </c>
       <c r="H85" t="n">
-        <v>1298</v>
+        <v>1274</v>
       </c>
       <c r="I85" t="inlineStr"/>
       <c r="J85" t="inlineStr"/>
@@ -19941,14 +19941,14 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>1299</v>
+        <v>1275</v>
       </c>
       <c r="B86" t="n">
-        <v>1212</v>
+        <v>1188</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>1xCUaRipzEBRjcRGOUa__w</t>
+          <t>0ydbChVXH5YeiOECwP0lP5</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -19972,7 +19972,7 @@
         </is>
       </c>
       <c r="H86" t="n">
-        <v>1299</v>
+        <v>1275</v>
       </c>
       <c r="I86" t="inlineStr"/>
       <c r="J86" t="inlineStr"/>
@@ -20004,7 +20004,7 @@
         </is>
       </c>
       <c r="AD86" t="n">
-        <v>11.947</v>
+        <v>11.948</v>
       </c>
       <c r="AE86" t="inlineStr"/>
       <c r="AF86" t="inlineStr"/>
@@ -20168,14 +20168,14 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>1300</v>
+        <v>1276</v>
       </c>
       <c r="B87" t="n">
-        <v>1209</v>
+        <v>1185</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>0x9I5spTf0W8z7GhPCk1ky</t>
+          <t>3tE0xz5ivFbule77FUWYT7</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -20199,7 +20199,7 @@
         </is>
       </c>
       <c r="H87" t="n">
-        <v>1300</v>
+        <v>1276</v>
       </c>
       <c r="I87" t="inlineStr"/>
       <c r="J87" t="inlineStr"/>
@@ -20341,13 +20341,13 @@
         <v>3</v>
       </c>
       <c r="CF87" t="n">
-        <v>70.77332838583099</v>
+        <v>70.7806751860665</v>
       </c>
       <c r="CG87" t="n">
-        <v>123.877062</v>
+        <v>123.8381265</v>
       </c>
       <c r="CH87" t="n">
-        <v>371.631186</v>
+        <v>371.5143795</v>
       </c>
       <c r="CI87" t="inlineStr">
         <is>
@@ -20377,7 +20377,7 @@
         <v>0</v>
       </c>
       <c r="CT87" t="n">
-        <v>123.877062</v>
+        <v>123.8381265</v>
       </c>
       <c r="CU87" t="n">
         <v>0</v>
@@ -20391,14 +20391,14 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>1301</v>
+        <v>1277</v>
       </c>
       <c r="B88" t="n">
-        <v>1208</v>
+        <v>1184</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>2goFLwB6DCTwDTgbAWEEIH</t>
+          <t>2gsiWFr2TB1AHTbv7ojX6m</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -20422,7 +20422,7 @@
         </is>
       </c>
       <c r="H88" t="n">
-        <v>1301</v>
+        <v>1277</v>
       </c>
       <c r="I88" t="inlineStr"/>
       <c r="J88" t="inlineStr"/>
@@ -20565,7 +20565,7 @@
         </is>
       </c>
       <c r="CE88" t="n">
-        <v>3.421</v>
+        <v>3.42</v>
       </c>
       <c r="CF88" t="n">
         <v>14.8495146387802</v>
@@ -20574,7 +20574,7 @@
         <v>9.246236</v>
       </c>
       <c r="CH88" t="n">
-        <v>31.631373356</v>
+        <v>31.62212712</v>
       </c>
       <c r="CI88" t="inlineStr">
         <is>
@@ -20618,14 +20618,14 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>1302</v>
+        <v>1278</v>
       </c>
       <c r="B89" t="n">
-        <v>1211</v>
+        <v>1187</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>0d65XwDRr8KPZICzeqHSW5</t>
+          <t>3jgApaggT6VOj2drGLqhV$</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -20649,7 +20649,7 @@
         </is>
       </c>
       <c r="H89" t="n">
-        <v>1302</v>
+        <v>1278</v>
       </c>
       <c r="I89" t="inlineStr"/>
       <c r="J89" t="inlineStr"/>
@@ -20681,7 +20681,7 @@
         </is>
       </c>
       <c r="AD89" t="n">
-        <v>7.939</v>
+        <v>7.94</v>
       </c>
       <c r="AE89" t="inlineStr"/>
       <c r="AF89" t="inlineStr"/>
@@ -20792,7 +20792,7 @@
         </is>
       </c>
       <c r="CE89" t="n">
-        <v>3.579</v>
+        <v>3.578</v>
       </c>
       <c r="CF89" t="n">
         <v>10.1779200252527</v>
@@ -20801,7 +20801,7 @@
         <v>6.381486</v>
       </c>
       <c r="CH89" t="n">
-        <v>22.839338394</v>
+        <v>22.832956908</v>
       </c>
       <c r="CI89" t="inlineStr">
         <is>
@@ -20845,14 +20845,14 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>1303</v>
+        <v>1279</v>
       </c>
       <c r="B90" t="n">
-        <v>1208</v>
+        <v>1184</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>0WJ65NDaH54RWZcOZo2hFz</t>
+          <t>0L$CPopvL2ng78uaCkxmd2</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -20876,7 +20876,7 @@
         </is>
       </c>
       <c r="H90" t="n">
-        <v>1303</v>
+        <v>1279</v>
       </c>
       <c r="I90" t="inlineStr"/>
       <c r="J90" t="inlineStr"/>
@@ -21019,7 +21019,7 @@
         </is>
       </c>
       <c r="CE90" t="n">
-        <v>3.421</v>
+        <v>3.42</v>
       </c>
       <c r="CF90" t="n">
         <v>16.1398401474132</v>
@@ -21028,7 +21028,7 @@
         <v>11.0386675</v>
       </c>
       <c r="CH90" t="n">
-        <v>37.7632815175</v>
+        <v>37.75224285</v>
       </c>
       <c r="CI90" t="inlineStr">
         <is>
@@ -21072,14 +21072,14 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>1304</v>
+        <v>1280</v>
       </c>
       <c r="B91" t="n">
-        <v>1211</v>
+        <v>1187</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>0DQARhKmnCX83BGrsfeEgq</t>
+          <t>2R0Ko1_rT45gQWRWnSw8Rh</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -21103,7 +21103,7 @@
         </is>
       </c>
       <c r="H91" t="n">
-        <v>1304</v>
+        <v>1280</v>
       </c>
       <c r="I91" t="inlineStr"/>
       <c r="J91" t="inlineStr"/>
@@ -21135,7 +21135,7 @@
         </is>
       </c>
       <c r="AD91" t="n">
-        <v>7.939</v>
+        <v>7.94</v>
       </c>
       <c r="AE91" t="inlineStr"/>
       <c r="AF91" t="inlineStr"/>
@@ -21246,7 +21246,7 @@
         </is>
       </c>
       <c r="CE91" t="n">
-        <v>3.579</v>
+        <v>3.578</v>
       </c>
       <c r="CF91" t="n">
         <v>8.90153516286427</v>
@@ -21255,7 +21255,7 @@
         <v>4.561436</v>
       </c>
       <c r="CH91" t="n">
-        <v>16.325379444</v>
+        <v>16.320818008</v>
       </c>
       <c r="CI91" t="inlineStr">
         <is>
@@ -21299,14 +21299,14 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>1305</v>
+        <v>1281</v>
       </c>
       <c r="B92" t="n">
-        <v>1209</v>
+        <v>1185</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>2jn0CO4WT6agpI_e3theVz</t>
+          <t>30_jhjUID1lOEnoZkbwPlR</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -21330,7 +21330,7 @@
         </is>
       </c>
       <c r="H92" t="n">
-        <v>1305</v>
+        <v>1281</v>
       </c>
       <c r="I92" t="inlineStr"/>
       <c r="J92" t="inlineStr"/>
@@ -21526,14 +21526,14 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>1306</v>
+        <v>1282</v>
       </c>
       <c r="B93" t="n">
-        <v>1209</v>
+        <v>1185</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>0R6CzIVUf9Xg$xY9ZGMPOI</t>
+          <t>3v_If9$uz3fwzdtVKMHQ8o</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -21557,7 +21557,7 @@
         </is>
       </c>
       <c r="H93" t="n">
-        <v>1306</v>
+        <v>1282</v>
       </c>
       <c r="I93" t="inlineStr"/>
       <c r="J93" t="inlineStr"/>
@@ -21749,14 +21749,14 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>1307</v>
+        <v>1283</v>
       </c>
       <c r="B94" t="n">
-        <v>1207</v>
+        <v>1183</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>2h61zMFo5AJAPRusVng_Xn</t>
+          <t>2g7lHgM9fCfeWFLbqCROTN</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -21780,7 +21780,7 @@
         </is>
       </c>
       <c r="H94" t="n">
-        <v>1307</v>
+        <v>1283</v>
       </c>
       <c r="I94" t="inlineStr"/>
       <c r="J94" t="inlineStr"/>
@@ -21890,13 +21890,13 @@
         <v>4.42</v>
       </c>
       <c r="CF94" t="n">
-        <v>123.779783200545</v>
+        <v>123.77898440477</v>
       </c>
       <c r="CG94" t="n">
-        <v>946.7568455000001</v>
+        <v>946.7966155</v>
       </c>
       <c r="CH94" t="n">
-        <v>4184.66525711</v>
+        <v>4184.84104051</v>
       </c>
       <c r="CI94" t="inlineStr"/>
       <c r="CJ94" t="inlineStr"/>
@@ -21912,7 +21912,7 @@
         </is>
       </c>
       <c r="CR94" t="n">
-        <v>946.7568455000001</v>
+        <v>946.7966155</v>
       </c>
       <c r="CS94" t="n">
         <v>0</v>
@@ -21932,14 +21932,14 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>1308</v>
+        <v>1284</v>
       </c>
       <c r="B95" t="n">
-        <v>1207</v>
+        <v>1183</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>1ocReKPMH6yQHek4DHBHWe</t>
+          <t>2TjpIVE3fEjf2yeWwF5tbt</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -21963,7 +21963,7 @@
         </is>
       </c>
       <c r="H95" t="n">
-        <v>1308</v>
+        <v>1284</v>
       </c>
       <c r="I95" t="inlineStr"/>
       <c r="J95" t="inlineStr"/>
@@ -22073,13 +22073,13 @@
         <v>0.5</v>
       </c>
       <c r="CF95" t="n">
-        <v>96.22017162882391</v>
+        <v>96.1953347530367</v>
       </c>
       <c r="CG95" t="n">
-        <v>946.748385</v>
+        <v>946.779711</v>
       </c>
       <c r="CH95" t="n">
-        <v>473.3741925</v>
+        <v>473.3898555</v>
       </c>
       <c r="CI95" t="inlineStr"/>
       <c r="CJ95" t="inlineStr"/>
@@ -22095,7 +22095,7 @@
         </is>
       </c>
       <c r="CR95" t="n">
-        <v>946.748385</v>
+        <v>946.779711</v>
       </c>
       <c r="CS95" t="n">
         <v>0</v>
@@ -22115,14 +22115,14 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>1309</v>
+        <v>1285</v>
       </c>
       <c r="B96" t="n">
-        <v>1207</v>
+        <v>1183</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>220mi7GG59YuA9V0nhWv8f</t>
+          <t>11rtg$OHHCQgjPenPfbWHc</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -22146,7 +22146,7 @@
         </is>
       </c>
       <c r="H96" t="n">
-        <v>1309</v>
+        <v>1285</v>
       </c>
       <c r="I96" t="inlineStr"/>
       <c r="J96" t="inlineStr"/>
@@ -22256,13 +22256,13 @@
         <v>1</v>
       </c>
       <c r="CF96" t="n">
-        <v>123.779783200545</v>
+        <v>123.77898440477</v>
       </c>
       <c r="CG96" t="n">
-        <v>946.7568455000001</v>
+        <v>946.7966155</v>
       </c>
       <c r="CH96" t="n">
-        <v>946.7568455000001</v>
+        <v>946.7966155</v>
       </c>
       <c r="CI96" t="inlineStr"/>
       <c r="CJ96" t="inlineStr"/>
@@ -22278,7 +22278,7 @@
         </is>
       </c>
       <c r="CR96" t="n">
-        <v>946.7568455000001</v>
+        <v>946.7966155</v>
       </c>
       <c r="CS96" t="n">
         <v>0</v>
@@ -22298,14 +22298,14 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>1310</v>
+        <v>1286</v>
       </c>
       <c r="B97" t="n">
-        <v>1208</v>
+        <v>1184</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>1WVo1W$JrFBwJk1Ud33P2_</t>
+          <t>37U7QqRiD3K8YpI0EDvqEG</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -22329,7 +22329,7 @@
         </is>
       </c>
       <c r="H97" t="n">
-        <v>1310</v>
+        <v>1286</v>
       </c>
       <c r="I97" t="inlineStr"/>
       <c r="J97" t="inlineStr"/>
@@ -22439,13 +22439,13 @@
         <v>3.78</v>
       </c>
       <c r="CF97" t="n">
-        <v>126.058990957543</v>
+        <v>126.05717405587</v>
       </c>
       <c r="CG97" t="n">
-        <v>944.3010395</v>
+        <v>944.3288025000001</v>
       </c>
       <c r="CH97" t="n">
-        <v>3569.45792931</v>
+        <v>3569.56287345</v>
       </c>
       <c r="CI97" t="inlineStr"/>
       <c r="CJ97" t="inlineStr"/>
@@ -22464,7 +22464,7 @@
         <v>0</v>
       </c>
       <c r="CS97" t="n">
-        <v>944.3010395</v>
+        <v>944.3288025000001</v>
       </c>
       <c r="CT97" t="n">
         <v>0</v>
@@ -22481,14 +22481,14 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>1311</v>
+        <v>1287</v>
       </c>
       <c r="B98" t="n">
-        <v>1208</v>
+        <v>1184</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>1CV6oaRyn1HQP8tN4myNln</t>
+          <t>1IKxMLTg96xBLZwOLJkOep</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -22512,7 +22512,7 @@
         </is>
       </c>
       <c r="H98" t="n">
-        <v>1311</v>
+        <v>1287</v>
       </c>
       <c r="I98" t="inlineStr"/>
       <c r="J98" t="inlineStr"/>
@@ -22622,13 +22622,13 @@
         <v>1</v>
       </c>
       <c r="CF98" t="n">
-        <v>126.058990957543</v>
+        <v>126.05717405587</v>
       </c>
       <c r="CG98" t="n">
-        <v>944.3010395</v>
+        <v>944.3288025000001</v>
       </c>
       <c r="CH98" t="n">
-        <v>944.3010395</v>
+        <v>944.3288025000001</v>
       </c>
       <c r="CI98" t="inlineStr"/>
       <c r="CJ98" t="inlineStr"/>
@@ -22647,7 +22647,7 @@
         <v>0</v>
       </c>
       <c r="CS98" t="n">
-        <v>944.3010395</v>
+        <v>944.3288025000001</v>
       </c>
       <c r="CT98" t="n">
         <v>0</v>
@@ -22664,14 +22664,14 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>1312</v>
+        <v>1288</v>
       </c>
       <c r="B99" t="n">
-        <v>1209</v>
+        <v>1185</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>3S19U$d1v2EAwMe1MFmPkg</t>
+          <t>1CcwMqeXT8UesKx8nLd6OD</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -22695,7 +22695,7 @@
         </is>
       </c>
       <c r="H99" t="n">
-        <v>1312</v>
+        <v>1288</v>
       </c>
       <c r="I99" t="inlineStr"/>
       <c r="J99" t="inlineStr"/>
@@ -22813,13 +22813,13 @@
         <v>1</v>
       </c>
       <c r="CF99" t="n">
-        <v>10.4510384173057</v>
+        <v>11.5343811888718</v>
       </c>
       <c r="CG99" t="n">
-        <v>6.8265125</v>
+        <v>10.45073</v>
       </c>
       <c r="CH99" t="n">
-        <v>6.8265125</v>
+        <v>10.45073</v>
       </c>
       <c r="CI99" t="inlineStr"/>
       <c r="CJ99" t="inlineStr"/>
@@ -22841,7 +22841,7 @@
         <v>0</v>
       </c>
       <c r="CT99" t="n">
-        <v>6.8265125</v>
+        <v>10.45073</v>
       </c>
       <c r="CU99" t="n">
         <v>0</v>
@@ -22855,14 +22855,14 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>1313</v>
+        <v>1289</v>
       </c>
       <c r="B100" t="n">
-        <v>1209</v>
+        <v>1185</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>1dO_bQkdz9nwDyTkTE7ib2</t>
+          <t>0XnoVHZ5b7YeZWNQ2bXPFm</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -22886,7 +22886,7 @@
         </is>
       </c>
       <c r="H100" t="n">
-        <v>1313</v>
+        <v>1289</v>
       </c>
       <c r="I100" t="inlineStr"/>
       <c r="J100" t="inlineStr"/>
@@ -23004,13 +23004,13 @@
         <v>1</v>
       </c>
       <c r="CF100" t="n">
-        <v>22.0715375602572</v>
+        <v>22.1434378257397</v>
       </c>
       <c r="CG100" t="n">
-        <v>16.361301</v>
+        <v>17.082447</v>
       </c>
       <c r="CH100" t="n">
-        <v>16.361301</v>
+        <v>17.082447</v>
       </c>
       <c r="CI100" t="inlineStr"/>
       <c r="CJ100" t="inlineStr"/>
@@ -23032,7 +23032,7 @@
         <v>0</v>
       </c>
       <c r="CT100" t="n">
-        <v>16.361301</v>
+        <v>17.082447</v>
       </c>
       <c r="CU100" t="n">
         <v>0</v>
@@ -23046,14 +23046,14 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>1314</v>
+        <v>1290</v>
       </c>
       <c r="B101" t="n">
-        <v>1209</v>
+        <v>1185</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>2tu7qWjqT2KwS8C7vq8SbN</t>
+          <t>3Phqv9RFv0aPLT5D_Im9QT</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -23077,7 +23077,7 @@
         </is>
       </c>
       <c r="H101" t="n">
-        <v>1314</v>
+        <v>1290</v>
       </c>
       <c r="I101" t="inlineStr"/>
       <c r="J101" t="inlineStr"/>
@@ -23187,13 +23187,13 @@
         <v>2.998</v>
       </c>
       <c r="CF101" t="n">
-        <v>110.604319237956</v>
+        <v>110.601345096434</v>
       </c>
       <c r="CG101" t="n">
-        <v>633.053385</v>
+        <v>633.1125025</v>
       </c>
       <c r="CH101" t="n">
-        <v>1897.89404823</v>
+        <v>1898.071282495</v>
       </c>
       <c r="CI101" t="inlineStr"/>
       <c r="CJ101" t="inlineStr"/>
@@ -23215,7 +23215,7 @@
         <v>0</v>
       </c>
       <c r="CT101" t="n">
-        <v>633.053385</v>
+        <v>633.1125025</v>
       </c>
       <c r="CU101" t="n">
         <v>0</v>
@@ -23229,14 +23229,14 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>1315</v>
+        <v>1291</v>
       </c>
       <c r="B102" t="n">
-        <v>1209</v>
+        <v>1185</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>2rXFWc8jX9X9uAiF4mg4_c</t>
+          <t>2CTrriW1D4XfbevcRhL0D$</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -23260,7 +23260,7 @@
         </is>
       </c>
       <c r="H102" t="n">
-        <v>1315</v>
+        <v>1291</v>
       </c>
       <c r="I102" t="inlineStr"/>
       <c r="J102" t="inlineStr"/>
@@ -23370,13 +23370,13 @@
         <v>0.66</v>
       </c>
       <c r="CF102" t="n">
-        <v>108.708999464787</v>
+        <v>108.706025323265</v>
       </c>
       <c r="CG102" t="n">
-        <v>635.4141235</v>
+        <v>635.473241</v>
       </c>
       <c r="CH102" t="n">
-        <v>419.37332151</v>
+        <v>419.41233906</v>
       </c>
       <c r="CI102" t="inlineStr"/>
       <c r="CJ102" t="inlineStr"/>
@@ -23398,7 +23398,7 @@
         <v>0</v>
       </c>
       <c r="CT102" t="n">
-        <v>635.4141235</v>
+        <v>635.473241</v>
       </c>
       <c r="CU102" t="n">
         <v>0</v>
@@ -23412,14 +23412,14 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>1316</v>
+        <v>1292</v>
       </c>
       <c r="B103" t="n">
-        <v>1209</v>
+        <v>1185</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>1xVbGem8z8Yw7KMlDD7tyl</t>
+          <t>3ue0$unPz0uux7AwL1STF3</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -23443,7 +23443,7 @@
         </is>
       </c>
       <c r="H103" t="n">
-        <v>1316</v>
+        <v>1292</v>
       </c>
       <c r="I103" t="inlineStr"/>
       <c r="J103" t="inlineStr"/>
@@ -23595,14 +23595,14 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>1317</v>
+        <v>1293</v>
       </c>
       <c r="B104" t="n">
-        <v>1209</v>
+        <v>1185</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>2JYUQcEU93zwiGeMtni83Z</t>
+          <t>2lJbeNWPr69PR6Bv8eHLx5</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -23626,7 +23626,7 @@
         </is>
       </c>
       <c r="H104" t="n">
-        <v>1317</v>
+        <v>1293</v>
       </c>
       <c r="I104" t="inlineStr"/>
       <c r="J104" t="inlineStr"/>
@@ -23736,13 +23736,13 @@
         <v>1</v>
       </c>
       <c r="CF104" t="n">
-        <v>108.708999464787</v>
+        <v>108.706025323265</v>
       </c>
       <c r="CG104" t="n">
-        <v>635.4141235</v>
+        <v>635.473241</v>
       </c>
       <c r="CH104" t="n">
-        <v>635.4141235</v>
+        <v>635.473241</v>
       </c>
       <c r="CI104" t="inlineStr"/>
       <c r="CJ104" t="inlineStr"/>
@@ -23764,7 +23764,7 @@
         <v>0</v>
       </c>
       <c r="CT104" t="n">
-        <v>635.4141235</v>
+        <v>635.473241</v>
       </c>
       <c r="CU104" t="n">
         <v>0</v>
@@ -23778,14 +23778,14 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>1318</v>
+        <v>1294</v>
       </c>
       <c r="B105" t="n">
-        <v>1210</v>
+        <v>1186</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>0cZezKqu94ovlQgVTxGUP9</t>
+          <t>1MQDEFDcX439MvQ3uigCM$</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -23809,7 +23809,7 @@
         </is>
       </c>
       <c r="H105" t="n">
-        <v>1318</v>
+        <v>1294</v>
       </c>
       <c r="I105" t="inlineStr"/>
       <c r="J105" t="inlineStr"/>
@@ -23924,16 +23924,16 @@
         </is>
       </c>
       <c r="CE105" t="n">
-        <v>1.158</v>
+        <v>0.999999999999999</v>
       </c>
       <c r="CF105" t="n">
-        <v>10.4510384173057</v>
+        <v>11.5343811888718</v>
       </c>
       <c r="CG105" t="n">
-        <v>6.8265125</v>
+        <v>10.45073</v>
       </c>
       <c r="CH105" t="n">
-        <v>7.90510147499999</v>
+        <v>10.45073</v>
       </c>
       <c r="CI105" t="inlineStr"/>
       <c r="CJ105" t="inlineStr"/>
@@ -23958,7 +23958,7 @@
         <v>0</v>
       </c>
       <c r="CU105" t="n">
-        <v>6.8265125</v>
+        <v>10.45073</v>
       </c>
       <c r="CV105" t="n">
         <v>0</v>
@@ -23969,14 +23969,14 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>1319</v>
+        <v>1295</v>
       </c>
       <c r="B106" t="n">
-        <v>1210</v>
+        <v>1186</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>1Bex$LLBz14RGCBVd_3SHQ</t>
+          <t>3aH$lMb654_u$4SW_WvFAN</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -24000,7 +24000,7 @@
         </is>
       </c>
       <c r="H106" t="n">
-        <v>1319</v>
+        <v>1295</v>
       </c>
       <c r="I106" t="inlineStr"/>
       <c r="J106" t="inlineStr"/>
@@ -24115,16 +24115,16 @@
         </is>
       </c>
       <c r="CE106" t="n">
-        <v>1.158</v>
+        <v>0.999999999999999</v>
       </c>
       <c r="CF106" t="n">
-        <v>27.2953812739153</v>
+        <v>27.4536844116549</v>
       </c>
       <c r="CG106" t="n">
-        <v>25.18441</v>
+        <v>25.384223</v>
       </c>
       <c r="CH106" t="n">
-        <v>29.16354678</v>
+        <v>25.384223</v>
       </c>
       <c r="CI106" t="inlineStr"/>
       <c r="CJ106" t="inlineStr"/>
@@ -24149,7 +24149,7 @@
         <v>0</v>
       </c>
       <c r="CU106" t="n">
-        <v>25.18441</v>
+        <v>25.384223</v>
       </c>
       <c r="CV106" t="n">
         <v>0</v>
@@ -24160,14 +24160,14 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>1320</v>
+        <v>1296</v>
       </c>
       <c r="B107" t="n">
-        <v>1210</v>
+        <v>1186</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>0s4lbBN6v2wQ56baFu8aCK</t>
+          <t>14l9pM3sL8xfYz1mvXCNWG</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -24191,7 +24191,7 @@
         </is>
       </c>
       <c r="H107" t="n">
-        <v>1320</v>
+        <v>1296</v>
       </c>
       <c r="I107" t="inlineStr"/>
       <c r="J107" t="inlineStr"/>
@@ -24306,16 +24306,16 @@
         </is>
       </c>
       <c r="CE107" t="n">
-        <v>1.158</v>
+        <v>0.999999999999999</v>
       </c>
       <c r="CF107" t="n">
-        <v>27.3237702962066</v>
+        <v>27.6473031566045</v>
       </c>
       <c r="CG107" t="n">
-        <v>25.3495095</v>
+        <v>25.882478</v>
       </c>
       <c r="CH107" t="n">
-        <v>29.354732001</v>
+        <v>25.882478</v>
       </c>
       <c r="CI107" t="inlineStr"/>
       <c r="CJ107" t="inlineStr"/>
@@ -24340,7 +24340,7 @@
         <v>0</v>
       </c>
       <c r="CU107" t="n">
-        <v>25.3495095</v>
+        <v>25.882478</v>
       </c>
       <c r="CV107" t="n">
         <v>0</v>
@@ -24351,14 +24351,14 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>1321</v>
+        <v>1297</v>
       </c>
       <c r="B108" t="n">
-        <v>1210</v>
+        <v>1186</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>29mRuo3Gj2kAoruOaOpQPk</t>
+          <t>0BPV577Cv2qOXbm$_0BLlX</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -24382,7 +24382,7 @@
         </is>
       </c>
       <c r="H108" t="n">
-        <v>1321</v>
+        <v>1297</v>
       </c>
       <c r="I108" t="inlineStr"/>
       <c r="J108" t="inlineStr"/>
@@ -24489,7 +24489,7 @@
       </c>
       <c r="CD108" t="inlineStr"/>
       <c r="CE108" t="n">
-        <v>4.281</v>
+        <v>4.282</v>
       </c>
       <c r="CF108" t="n">
         <v>104.920885573921</v>
@@ -24498,7 +24498,7 @@
         <v>607.3553475</v>
       </c>
       <c r="CH108" t="n">
-        <v>2600.0882426475</v>
+        <v>2600.695597995</v>
       </c>
       <c r="CI108" t="inlineStr"/>
       <c r="CJ108" t="inlineStr"/>
@@ -24534,14 +24534,14 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>1322</v>
+        <v>1298</v>
       </c>
       <c r="B109" t="n">
-        <v>1210</v>
+        <v>1186</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>2UYbzXfWX4jeekEZZounLu</t>
+          <t>0D49X8G8b21vMvV9fI6DYy</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -24565,7 +24565,7 @@
         </is>
       </c>
       <c r="H109" t="n">
-        <v>1322</v>
+        <v>1298</v>
       </c>
       <c r="I109" t="inlineStr"/>
       <c r="J109" t="inlineStr"/>
@@ -24717,14 +24717,14 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>1323</v>
+        <v>1299</v>
       </c>
       <c r="B110" t="n">
-        <v>1210</v>
+        <v>1186</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>2iqV3awXnFaPEu0T7HAtp4</t>
+          <t>3QbhoocVL16heqVtso3nIe</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -24748,7 +24748,7 @@
         </is>
       </c>
       <c r="H110" t="n">
-        <v>1323</v>
+        <v>1299</v>
       </c>
       <c r="I110" t="inlineStr"/>
       <c r="J110" t="inlineStr"/>
@@ -24900,14 +24900,14 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>1324</v>
+        <v>1300</v>
       </c>
       <c r="B111" t="n">
-        <v>1210</v>
+        <v>1186</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>2O9cNxLZXB48ei75HpXuVM</t>
+          <t>0sM00mZHr6DOEYTFqh$IrG</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -24931,7 +24931,7 @@
         </is>
       </c>
       <c r="H111" t="n">
-        <v>1324</v>
+        <v>1300</v>
       </c>
       <c r="I111" t="inlineStr"/>
       <c r="J111" t="inlineStr"/>
@@ -25083,14 +25083,14 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>1325</v>
+        <v>1301</v>
       </c>
       <c r="B112" t="n">
-        <v>1211</v>
+        <v>1187</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>19fOi9h4H1XBR85Agg_fkE</t>
+          <t>0hYc3lmMH2T91sw96db3JM</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -25114,7 +25114,7 @@
         </is>
       </c>
       <c r="H112" t="n">
-        <v>1325</v>
+        <v>1301</v>
       </c>
       <c r="I112" t="inlineStr"/>
       <c r="J112" t="inlineStr"/>
@@ -25146,7 +25146,7 @@
         </is>
       </c>
       <c r="AD112" t="n">
-        <v>7.939</v>
+        <v>7.94</v>
       </c>
       <c r="AE112" t="inlineStr"/>
       <c r="AF112" t="inlineStr"/>
@@ -25229,16 +25229,16 @@
         </is>
       </c>
       <c r="CE112" t="n">
-        <v>1.001</v>
+        <v>1</v>
       </c>
       <c r="CF112" t="n">
-        <v>28.2538110740109</v>
+        <v>28.3136803768729</v>
       </c>
       <c r="CG112" t="n">
-        <v>28.464383</v>
+        <v>28.4057145</v>
       </c>
       <c r="CH112" t="n">
-        <v>28.4928473830001</v>
+        <v>28.4057145000001</v>
       </c>
       <c r="CI112" t="inlineStr"/>
       <c r="CJ112" t="inlineStr"/>
@@ -25266,7 +25266,7 @@
         <v>0</v>
       </c>
       <c r="CV112" t="n">
-        <v>28.464383</v>
+        <v>28.4057145</v>
       </c>
       <c r="CW112" t="n">
         <v>0</v>
@@ -25274,14 +25274,14 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>1326</v>
+        <v>1302</v>
       </c>
       <c r="B113" t="n">
-        <v>1211</v>
+        <v>1187</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>1YjQd29ADBdhHAaWT8IdQR</t>
+          <t>0pnXM2gsT77R5nDFj8mzSx</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -25305,7 +25305,7 @@
         </is>
       </c>
       <c r="H113" t="n">
-        <v>1326</v>
+        <v>1302</v>
       </c>
       <c r="I113" t="inlineStr"/>
       <c r="J113" t="inlineStr"/>
@@ -25337,7 +25337,7 @@
         </is>
       </c>
       <c r="AD113" t="n">
-        <v>7.939</v>
+        <v>7.94</v>
       </c>
       <c r="AE113" t="inlineStr"/>
       <c r="AF113" t="inlineStr"/>
@@ -25420,16 +25420,16 @@
         </is>
       </c>
       <c r="CE113" t="n">
-        <v>1.001</v>
+        <v>1</v>
       </c>
       <c r="CF113" t="n">
-        <v>28.2852454986017</v>
+        <v>28.4471992015421</v>
       </c>
       <c r="CG113" t="n">
-        <v>28.6278645</v>
+        <v>29.2135305</v>
       </c>
       <c r="CH113" t="n">
-        <v>28.6564923645001</v>
+        <v>29.2135305000001</v>
       </c>
       <c r="CI113" t="inlineStr"/>
       <c r="CJ113" t="inlineStr"/>
@@ -25457,7 +25457,7 @@
         <v>0</v>
       </c>
       <c r="CV113" t="n">
-        <v>28.6278645</v>
+        <v>29.2135305</v>
       </c>
       <c r="CW113" t="n">
         <v>0</v>
@@ -25465,14 +25465,14 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>1327</v>
+        <v>1303</v>
       </c>
       <c r="B114" t="n">
-        <v>1211</v>
+        <v>1187</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>0Dg5sNnYTBWwyKrJUXkFTO</t>
+          <t>2$k1ahqBDFJPjWMBdR8WtC</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -25496,7 +25496,7 @@
         </is>
       </c>
       <c r="H114" t="n">
-        <v>1327</v>
+        <v>1303</v>
       </c>
       <c r="I114" t="inlineStr"/>
       <c r="J114" t="inlineStr"/>
@@ -25528,7 +25528,7 @@
         </is>
       </c>
       <c r="AD114" t="n">
-        <v>7.939</v>
+        <v>7.94</v>
       </c>
       <c r="AE114" t="inlineStr"/>
       <c r="AF114" t="inlineStr"/>
@@ -25611,16 +25611,16 @@
         </is>
       </c>
       <c r="CE114" t="n">
-        <v>1.001</v>
+        <v>1</v>
       </c>
       <c r="CF114" t="n">
-        <v>10.4510384173057</v>
+        <v>11.5343811888718</v>
       </c>
       <c r="CG114" t="n">
-        <v>6.8265125</v>
+        <v>10.45073</v>
       </c>
       <c r="CH114" t="n">
-        <v>6.83333901250001</v>
+        <v>10.45073</v>
       </c>
       <c r="CI114" t="inlineStr"/>
       <c r="CJ114" t="inlineStr"/>
@@ -25648,7 +25648,7 @@
         <v>0</v>
       </c>
       <c r="CV114" t="n">
-        <v>6.8265125</v>
+        <v>10.45073</v>
       </c>
       <c r="CW114" t="n">
         <v>0</v>
@@ -25656,14 +25656,14 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>1328</v>
+        <v>1304</v>
       </c>
       <c r="B115" t="n">
-        <v>1211</v>
+        <v>1187</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>2HDdALzov8sOiati08LIYR</t>
+          <t>1vS9xL68j7QRd7X5GTAvLE</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -25687,7 +25687,7 @@
         </is>
       </c>
       <c r="H115" t="n">
-        <v>1328</v>
+        <v>1304</v>
       </c>
       <c r="I115" t="inlineStr"/>
       <c r="J115" t="inlineStr"/>
@@ -25719,7 +25719,7 @@
         </is>
       </c>
       <c r="AD115" t="n">
-        <v>7.939</v>
+        <v>7.94</v>
       </c>
       <c r="AE115" t="inlineStr"/>
       <c r="AF115" t="inlineStr"/>
@@ -25794,7 +25794,7 @@
       </c>
       <c r="CD115" t="inlineStr"/>
       <c r="CE115" t="n">
-        <v>4.009</v>
+        <v>4.008</v>
       </c>
       <c r="CF115" t="n">
         <v>104.909626929904</v>
@@ -25803,7 +25803,7 @@
         <v>607.3728175</v>
       </c>
       <c r="CH115" t="n">
-        <v>2434.9576253575</v>
+        <v>2434.35025254</v>
       </c>
       <c r="CI115" t="inlineStr"/>
       <c r="CJ115" t="inlineStr"/>
@@ -25839,14 +25839,14 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>1329</v>
+        <v>1305</v>
       </c>
       <c r="B116" t="n">
-        <v>1211</v>
+        <v>1187</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>2E_TZJZ7r4DgKH0p0YQJl8</t>
+          <t>0rjMKvNtzAnefNaYJ97j52</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -25870,7 +25870,7 @@
         </is>
       </c>
       <c r="H116" t="n">
-        <v>1329</v>
+        <v>1305</v>
       </c>
       <c r="I116" t="inlineStr"/>
       <c r="J116" t="inlineStr"/>
@@ -25902,7 +25902,7 @@
         </is>
       </c>
       <c r="AD116" t="n">
-        <v>7.939</v>
+        <v>7.94</v>
       </c>
       <c r="AE116" t="inlineStr"/>
       <c r="AF116" t="inlineStr"/>
@@ -26022,14 +26022,14 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>1330</v>
+        <v>1306</v>
       </c>
       <c r="B117" t="n">
-        <v>1212</v>
+        <v>1188</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>3eXcdEMUX3XuwJXhU1bBiW</t>
+          <t>3r8c5tGbPC_fDRkxzKA81G</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -26053,7 +26053,7 @@
         </is>
       </c>
       <c r="H117" t="n">
-        <v>1330</v>
+        <v>1306</v>
       </c>
       <c r="I117" t="inlineStr"/>
       <c r="J117" t="inlineStr"/>
@@ -26085,7 +26085,7 @@
         </is>
       </c>
       <c r="AD117" t="n">
-        <v>11.947</v>
+        <v>11.948</v>
       </c>
       <c r="AE117" t="inlineStr"/>
       <c r="AF117" t="inlineStr"/>
@@ -26168,16 +26168,16 @@
         </is>
       </c>
       <c r="CE117" t="n">
-        <v>1.001</v>
+        <v>1</v>
       </c>
       <c r="CF117" t="n">
-        <v>10.4510384173057</v>
+        <v>11.5343811888718</v>
       </c>
       <c r="CG117" t="n">
-        <v>6.8265125</v>
+        <v>10.45073</v>
       </c>
       <c r="CH117" t="n">
-        <v>6.8333390125</v>
+        <v>10.45073</v>
       </c>
       <c r="CI117" t="inlineStr"/>
       <c r="CJ117" t="inlineStr"/>
@@ -26208,19 +26208,19 @@
         <v>0</v>
       </c>
       <c r="CW117" t="n">
-        <v>6.8265125</v>
+        <v>10.45073</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>1331</v>
+        <v>1307</v>
       </c>
       <c r="B118" t="n">
-        <v>1212</v>
+        <v>1188</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>2yWWAdHcT0Ee9Cxo9n9g3E</t>
+          <t>3hhMFg80L1LfBHM_a3hr7A</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -26244,7 +26244,7 @@
         </is>
       </c>
       <c r="H118" t="n">
-        <v>1331</v>
+        <v>1307</v>
       </c>
       <c r="I118" t="inlineStr"/>
       <c r="J118" t="inlineStr"/>
@@ -26276,7 +26276,7 @@
         </is>
       </c>
       <c r="AD118" t="n">
-        <v>11.947</v>
+        <v>11.948</v>
       </c>
       <c r="AE118" t="inlineStr"/>
       <c r="AF118" t="inlineStr"/>
@@ -26359,16 +26359,16 @@
         </is>
       </c>
       <c r="CE118" t="n">
-        <v>1.001</v>
+        <v>0.999999999999998</v>
       </c>
       <c r="CF118" t="n">
-        <v>29.8805721692127</v>
+        <v>29.8929803703454</v>
       </c>
       <c r="CG118" t="n">
-        <v>40.6284265</v>
+        <v>40.5779875</v>
       </c>
       <c r="CH118" t="n">
-        <v>40.6690549264999</v>
+        <v>40.5779874999999</v>
       </c>
       <c r="CI118" t="inlineStr"/>
       <c r="CJ118" t="inlineStr"/>
@@ -26399,19 +26399,19 @@
         <v>0</v>
       </c>
       <c r="CW118" t="n">
-        <v>40.6284265</v>
+        <v>40.5779875</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>1332</v>
+        <v>1308</v>
       </c>
       <c r="B119" t="n">
-        <v>1212</v>
+        <v>1188</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>191C_eUqLBjwUYQYjuyzbJ</t>
+          <t>1MeUygKbr5gwqhdLnI1$fr</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -26435,7 +26435,7 @@
         </is>
       </c>
       <c r="H119" t="n">
-        <v>1332</v>
+        <v>1308</v>
       </c>
       <c r="I119" t="inlineStr"/>
       <c r="J119" t="inlineStr"/>
@@ -26467,7 +26467,7 @@
         </is>
       </c>
       <c r="AD119" t="n">
-        <v>11.947</v>
+        <v>11.948</v>
       </c>
       <c r="AE119" t="inlineStr"/>
       <c r="AF119" t="inlineStr"/>
@@ -26587,14 +26587,14 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>1333</v>
+        <v>1309</v>
       </c>
       <c r="B120" t="n">
-        <v>1212</v>
+        <v>1188</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>1AmWYBKrzAYQ$BPe2iH8In</t>
+          <t>0qFk07a55D6POPpcM5bCmf</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -26618,7 +26618,7 @@
         </is>
       </c>
       <c r="H120" t="n">
-        <v>1333</v>
+        <v>1309</v>
       </c>
       <c r="I120" t="inlineStr"/>
       <c r="J120" t="inlineStr"/>
@@ -26650,7 +26650,7 @@
         </is>
       </c>
       <c r="AD120" t="n">
-        <v>11.947</v>
+        <v>11.948</v>
       </c>
       <c r="AE120" t="inlineStr"/>
       <c r="AF120" t="inlineStr"/>
